--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_glass.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_glass.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="34">
   <si>
     <t>configuracion</t>
   </si>
@@ -570,10 +570,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H2">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L2" t="s">
         <v>29</v>
@@ -623,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -635,11 +641,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
       </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L3" t="s">
         <v>28</v>
       </c>
@@ -656,7 +668,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
@@ -700,11 +712,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I4" t="s">
         <v>15</v>
       </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L4" t="s">
         <v>32</v>
       </c>
@@ -721,7 +739,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -765,10 +783,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I5" t="s">
         <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5" t="s">
         <v>29</v>
@@ -830,10 +854,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I6" t="s">
         <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L6" t="s">
         <v>32</v>
@@ -895,10 +925,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H7">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I7" t="s">
         <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
       </c>
       <c r="L7" t="s">
         <v>29</v>
@@ -960,10 +996,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H8">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L8" t="s">
         <v>28</v>
@@ -1025,10 +1067,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H9">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L9" t="s">
         <v>28</v>
@@ -1090,10 +1138,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H10">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L10" t="s">
         <v>28</v>
@@ -1155,10 +1209,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
       </c>
       <c r="L11" t="s">
         <v>29</v>
@@ -1220,10 +1280,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H12">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I12" t="s">
         <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
       </c>
       <c r="L12" t="s">
         <v>29</v>
@@ -1273,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -1285,11 +1351,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H13">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I13" t="s">
         <v>15</v>
       </c>
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L13" t="s">
         <v>28</v>
       </c>
@@ -1306,7 +1378,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="b">
         <v>1</v>
@@ -1318,7 +1390,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1338,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1350,11 +1422,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H14">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I14" t="s">
         <v>15</v>
       </c>
+      <c r="J14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L14" t="s">
         <v>27</v>
       </c>
@@ -1371,7 +1449,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
@@ -1403,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1415,11 +1493,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H15">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I15" t="s">
         <v>15</v>
       </c>
+      <c r="J15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L15" t="s">
         <v>28</v>
       </c>
@@ -1436,7 +1520,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="b">
         <v>1</v>
@@ -1448,7 +1532,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1480,10 +1564,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H16">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I16" t="s">
         <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L16" t="s">
         <v>33</v>
@@ -1545,10 +1635,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H17">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L17" t="s">
         <v>30</v>
@@ -1610,10 +1706,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H18">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
       </c>
       <c r="L18" t="s">
         <v>28</v>
@@ -1675,10 +1777,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H19">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I19" t="s">
         <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L19" t="s">
         <v>28</v>
@@ -1740,11 +1848,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H20">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I20" t="s">
         <v>15</v>
       </c>
+      <c r="J20" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L20" t="s">
         <v>32</v>
       </c>
@@ -1761,7 +1875,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="b">
         <v>0</v>
@@ -1805,10 +1919,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H21">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I21" t="s">
         <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L21" t="s">
         <v>28</v>
@@ -1870,10 +1990,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H22">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L22" t="s">
         <v>28</v>
@@ -1923,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -1935,11 +2061,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H23">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I23" t="s">
         <v>15</v>
       </c>
+      <c r="J23" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L23" t="s">
         <v>28</v>
       </c>
@@ -1956,7 +2088,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
@@ -1988,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2000,11 +2132,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H24">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I24" t="s">
         <v>15</v>
       </c>
+      <c r="J24" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L24" t="s">
         <v>28</v>
       </c>
@@ -2021,7 +2159,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
@@ -2033,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2065,11 +2203,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H25">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I25" t="s">
         <v>15</v>
       </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L25" t="s">
         <v>26</v>
       </c>
@@ -2086,7 +2230,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -2130,10 +2274,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H26">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I26" t="s">
         <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>28</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
       </c>
       <c r="L26" t="s">
         <v>28</v>
@@ -2195,10 +2345,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H27">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I27" t="s">
         <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L27" t="s">
         <v>28</v>
@@ -2248,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -2260,11 +2416,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H28">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I28" t="s">
         <v>15</v>
       </c>
+      <c r="J28" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L28" t="s">
         <v>28</v>
       </c>
@@ -2281,7 +2443,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="b">
         <v>1</v>
@@ -2325,10 +2487,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H29">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I29" t="s">
         <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
       </c>
       <c r="L29" t="s">
         <v>28</v>
@@ -2390,10 +2558,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H30">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I30" t="s">
         <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -2455,11 +2629,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H31">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I31" t="s">
         <v>15</v>
       </c>
+      <c r="J31" t="s">
+        <v>28</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
       <c r="L31" t="s">
         <v>28</v>
       </c>
@@ -2488,7 +2668,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -2520,10 +2700,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H32">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I32" t="s">
         <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>28</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
       </c>
       <c r="L32" t="s">
         <v>28</v>
@@ -2585,10 +2771,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H33">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I33" t="s">
         <v>15</v>
+      </c>
+      <c r="J33" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -2650,10 +2842,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H34">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I34" t="s">
         <v>15</v>
+      </c>
+      <c r="J34" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L34" t="s">
         <v>28</v>
@@ -2715,10 +2913,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H35">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I35" t="s">
         <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L35" t="s">
         <v>28</v>
@@ -2780,11 +2984,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H36">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I36" t="s">
         <v>15</v>
       </c>
+      <c r="J36" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L36" t="s">
         <v>28</v>
       </c>
@@ -2801,7 +3011,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="b">
         <v>1</v>
@@ -2845,10 +3055,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H37">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I37" t="s">
         <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>28</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
       </c>
       <c r="L37" t="s">
         <v>28</v>
@@ -2910,10 +3126,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H38">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I38" t="s">
         <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>28</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
       </c>
       <c r="L38" t="s">
         <v>33</v>
@@ -2975,11 +3197,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H39">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I39" t="s">
         <v>15</v>
       </c>
+      <c r="J39" t="s">
+        <v>28</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
       <c r="L39" t="s">
         <v>28</v>
       </c>
@@ -3008,7 +3236,7 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -3040,11 +3268,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H40">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I40" t="s">
         <v>15</v>
       </c>
+      <c r="J40" t="s">
+        <v>28</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
       <c r="L40" t="s">
         <v>28</v>
       </c>
@@ -3073,7 +3307,7 @@
         <v>7</v>
       </c>
       <c r="U40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3105,10 +3339,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H41">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I41" t="s">
         <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>28</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
       </c>
       <c r="L41" t="s">
         <v>33</v>
@@ -3170,10 +3410,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H42">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I42" t="s">
         <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>28</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
       </c>
       <c r="L42" t="s">
         <v>28</v>
@@ -3235,10 +3481,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H43">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I43" t="s">
         <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L43" t="s">
         <v>28</v>
@@ -3300,10 +3552,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H44">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I44" t="s">
         <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L44" t="s">
         <v>29</v>
@@ -3365,10 +3623,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H45">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I45" t="s">
         <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L45" t="s">
         <v>28</v>
@@ -3430,10 +3694,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H46">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I46" t="s">
         <v>15</v>
+      </c>
+      <c r="J46" t="s">
+        <v>26</v>
+      </c>
+      <c r="K46">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L46" t="s">
         <v>28</v>
@@ -3495,11 +3765,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H47">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I47" t="s">
         <v>15</v>
       </c>
+      <c r="J47" t="s">
+        <v>28</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
       <c r="L47" t="s">
         <v>28</v>
       </c>
@@ -3528,7 +3804,7 @@
         <v>7</v>
       </c>
       <c r="U47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47">
         <v>7</v>
@@ -3560,11 +3836,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H48">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I48" t="s">
         <v>15</v>
       </c>
+      <c r="J48" t="s">
+        <v>27</v>
+      </c>
+      <c r="K48">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="L48" t="s">
         <v>31</v>
       </c>
@@ -3581,7 +3863,7 @@
         <v>0.5916727785823275</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
@@ -3625,10 +3907,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H49">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I49" t="s">
         <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L49" t="s">
         <v>26</v>
@@ -3690,10 +3978,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H50">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I50" t="s">
         <v>15</v>
+      </c>
+      <c r="J50" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50">
+        <v>0.5714285714285714</v>
       </c>
       <c r="L50" t="s">
         <v>28</v>
@@ -3755,11 +4049,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H51">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I51" t="s">
         <v>15</v>
       </c>
+      <c r="J51" t="s">
+        <v>28</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
       <c r="L51" t="s">
         <v>28</v>
       </c>
@@ -3788,7 +4088,7 @@
         <v>7</v>
       </c>
       <c r="U51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V51">
         <v>7</v>
@@ -3820,10 +4120,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H52">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I52" t="s">
         <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>30</v>
+      </c>
+      <c r="K52">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L52" t="s">
         <v>28</v>
@@ -3885,10 +4191,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H53">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I53" t="s">
         <v>15</v>
+      </c>
+      <c r="J53" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L53" t="s">
         <v>28</v>
@@ -3950,10 +4262,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H54">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I54" t="s">
         <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L54" t="s">
         <v>28</v>
@@ -4015,11 +4333,17 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H55">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I55" t="s">
         <v>15</v>
       </c>
+      <c r="J55" t="s">
+        <v>28</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
       <c r="L55" t="s">
         <v>28</v>
       </c>
@@ -4048,7 +4372,7 @@
         <v>7</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55">
         <v>7</v>
@@ -4080,10 +4404,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H56">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I56" t="s">
         <v>15</v>
+      </c>
+      <c r="J56" t="s">
+        <v>26</v>
+      </c>
+      <c r="K56">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L56" t="s">
         <v>32</v>
@@ -4145,10 +4475,16 @@
         <v>0.5817985234708472</v>
       </c>
       <c r="H57">
-        <v>0.3</v>
+        <v>0.5916727785823275</v>
       </c>
       <c r="I57" t="s">
         <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>26</v>
+      </c>
+      <c r="K57">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L57" t="s">
         <v>26</v>
@@ -4210,10 +4546,16 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H58">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I58" t="s">
         <v>15</v>
+      </c>
+      <c r="J58" t="s">
+        <v>32</v>
+      </c>
+      <c r="K58">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L58" t="s">
         <v>28</v>
@@ -4275,11 +4617,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H59">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I59" t="s">
         <v>15</v>
       </c>
+      <c r="J59" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L59" t="s">
         <v>28</v>
       </c>
@@ -4296,7 +4644,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="b">
         <v>1</v>
@@ -4340,11 +4688,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H60">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I60" t="s">
         <v>15</v>
       </c>
+      <c r="J60" t="s">
+        <v>33</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
       <c r="L60" t="s">
         <v>33</v>
       </c>
@@ -4361,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
@@ -4405,11 +4759,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H61">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I61" t="s">
         <v>15</v>
       </c>
+      <c r="J61" t="s">
+        <v>31</v>
+      </c>
+      <c r="K61">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L61" t="s">
         <v>26</v>
       </c>
@@ -4426,7 +4786,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
@@ -4470,10 +4830,16 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H62">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I62" t="s">
         <v>15</v>
+      </c>
+      <c r="J62" t="s">
+        <v>32</v>
+      </c>
+      <c r="K62">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L62" t="s">
         <v>27</v>
@@ -4535,11 +4901,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H63">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I63" t="s">
         <v>15</v>
       </c>
+      <c r="J63" t="s">
+        <v>33</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
       <c r="L63" t="s">
         <v>26</v>
       </c>
@@ -4556,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
@@ -4600,10 +4972,16 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H64">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I64" t="s">
         <v>15</v>
+      </c>
+      <c r="J64" t="s">
+        <v>32</v>
+      </c>
+      <c r="K64">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L64" t="s">
         <v>28</v>
@@ -4665,10 +5043,16 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H65">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I65" t="s">
         <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>32</v>
+      </c>
+      <c r="K65">
+        <v>0.2857142857142857</v>
       </c>
       <c r="L65" t="s">
         <v>28</v>
@@ -4730,11 +5114,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H66">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I66" t="s">
         <v>15</v>
       </c>
+      <c r="J66" t="s">
+        <v>31</v>
+      </c>
+      <c r="K66">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L66" t="s">
         <v>28</v>
       </c>
@@ -4751,7 +5141,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="b">
         <v>1</v>
@@ -4795,11 +5185,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H67">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I67" t="s">
         <v>15</v>
       </c>
+      <c r="J67" t="s">
+        <v>33</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
       <c r="L67" t="s">
         <v>28</v>
       </c>
@@ -4816,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="b">
         <v>1</v>
@@ -4848,7 +5244,7 @@
         <v>3</v>
       </c>
       <c r="D68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>7</v>
@@ -4860,11 +5256,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H68">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I68" t="s">
         <v>15</v>
       </c>
+      <c r="J68" t="s">
+        <v>33</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
       <c r="L68" t="s">
         <v>28</v>
       </c>
@@ -4881,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="b">
         <v>1</v>
@@ -4925,11 +5327,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H69">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I69" t="s">
         <v>15</v>
       </c>
+      <c r="J69" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L69" t="s">
         <v>33</v>
       </c>
@@ -4946,7 +5354,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
@@ -4990,11 +5398,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H70">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I70" t="s">
         <v>15</v>
       </c>
+      <c r="J70" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70">
+        <v>0.1428571428571428</v>
+      </c>
       <c r="L70" t="s">
         <v>28</v>
       </c>
@@ -5011,7 +5425,7 @@
         <v>0.5916727785823273</v>
       </c>
       <c r="Q70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="b">
         <v>1</v>
@@ -5043,7 +5457,7 @@
         <v>3</v>
       </c>
       <c r="D71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>7</v>
@@ -5055,11 +5469,17 @@
         <v>0.8048962451751512</v>
       </c>
       <c r="H71">
-        <v>0.3</v>
+        <v>0.5916727785823273</v>
       </c>
       <c r="I71" t="s">
         <v>15</v>
       </c>
+      <c r="J71" t="s">
+        <v>33</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
       <c r="L71" t="s">
         <v>27</v>
       </c>
@@ -5076,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="Q71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="b">
         <v>1</v>
@@ -5120,11 +5540,17 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H72">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
       </c>
+      <c r="J72" t="s">
+        <v>33</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
       <c r="L72" t="s">
         <v>31</v>
       </c>
@@ -5141,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="Q72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
@@ -5185,11 +5611,17 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H73">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I73" t="s">
         <v>15</v>
       </c>
+      <c r="J73" t="s">
+        <v>26</v>
+      </c>
+      <c r="K73">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="L73" t="s">
         <v>28</v>
       </c>
@@ -5206,7 +5638,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="b">
         <v>1</v>
@@ -5250,10 +5682,16 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H74">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I74" t="s">
         <v>15</v>
+      </c>
+      <c r="J74" t="s">
+        <v>30</v>
+      </c>
+      <c r="K74">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L74" t="s">
         <v>28</v>
@@ -5303,7 +5741,7 @@
         <v>5</v>
       </c>
       <c r="D75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75">
         <v>7</v>
@@ -5315,11 +5753,17 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H75">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
       </c>
+      <c r="J75" t="s">
+        <v>26</v>
+      </c>
+      <c r="K75">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="L75" t="s">
         <v>28</v>
       </c>
@@ -5336,7 +5780,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -5348,7 +5792,7 @@
         <v>7</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V75">
         <v>7</v>
@@ -5380,11 +5824,17 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H76">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I76" t="s">
         <v>15</v>
       </c>
+      <c r="J76" t="s">
+        <v>33</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
       <c r="L76" t="s">
         <v>28</v>
       </c>
@@ -5401,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
@@ -5445,11 +5895,17 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H77">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I77" t="s">
         <v>15</v>
       </c>
+      <c r="J77" t="s">
+        <v>32</v>
+      </c>
+      <c r="K77">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L77" t="s">
         <v>33</v>
       </c>
@@ -5466,7 +5922,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
@@ -5498,7 +5954,7 @@
         <v>5</v>
       </c>
       <c r="D78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>7</v>
@@ -5510,11 +5966,17 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H78">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I78" t="s">
         <v>15</v>
       </c>
+      <c r="J78" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78">
+        <v>0.7142857142857143</v>
+      </c>
       <c r="L78" t="s">
         <v>28</v>
       </c>
@@ -5531,7 +5993,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="b">
         <v>1</v>
@@ -5543,7 +6005,7 @@
         <v>7</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V78">
         <v>7</v>
@@ -5563,7 +6025,7 @@
         <v>5</v>
       </c>
       <c r="D79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79">
         <v>7</v>
@@ -5575,11 +6037,17 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H79">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I79" t="s">
         <v>15</v>
       </c>
+      <c r="J79" t="s">
+        <v>33</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
       <c r="L79" t="s">
         <v>27</v>
       </c>
@@ -5596,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="Q79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="b">
         <v>1</v>
@@ -5640,10 +6108,16 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H80">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I80" t="s">
         <v>15</v>
+      </c>
+      <c r="J80" t="s">
+        <v>30</v>
+      </c>
+      <c r="K80">
+        <v>0.4285714285714285</v>
       </c>
       <c r="L80" t="s">
         <v>28</v>
@@ -5693,7 +6167,7 @@
         <v>5</v>
       </c>
       <c r="D81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81">
         <v>7</v>
@@ -5705,11 +6179,17 @@
         <v>2.838098186555688</v>
       </c>
       <c r="H81">
-        <v>0.3</v>
+        <v>0.863120568566631</v>
       </c>
       <c r="I81" t="s">
         <v>15</v>
       </c>
+      <c r="J81" t="s">
+        <v>32</v>
+      </c>
+      <c r="K81">
+        <v>0.2857142857142857</v>
+      </c>
       <c r="L81" t="s">
         <v>28</v>
       </c>
@@ -5726,7 +6206,7 @@
         <v>0.863120568566631</v>
       </c>
       <c r="Q81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" t="b">
         <v>1</v>
@@ -5738,7 +6218,7 @@
         <v>7</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V81">
         <v>7</v>
@@ -5770,11 +6250,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H82">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I82" t="s">
         <v>15</v>
       </c>
+      <c r="J82" t="s">
+        <v>33</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
       <c r="L82" t="s">
         <v>33</v>
       </c>
@@ -5791,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="b">
         <v>0</v>
@@ -5823,7 +6309,7 @@
         <v>7</v>
       </c>
       <c r="D83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>7</v>
@@ -5835,11 +6321,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H83">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I83" t="s">
         <v>15</v>
       </c>
+      <c r="J83" t="s">
+        <v>33</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
       <c r="L83" t="s">
         <v>28</v>
       </c>
@@ -5856,7 +6348,7 @@
         <v>0</v>
       </c>
       <c r="Q83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="b">
         <v>1</v>
@@ -5900,11 +6392,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H84">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I84" t="s">
         <v>15</v>
       </c>
+      <c r="J84" t="s">
+        <v>28</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
       <c r="L84" t="s">
         <v>28</v>
       </c>
@@ -5933,7 +6431,7 @@
         <v>7</v>
       </c>
       <c r="U84">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V84">
         <v>7</v>
@@ -5965,11 +6463,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H85">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I85" t="s">
         <v>15</v>
       </c>
+      <c r="J85" t="s">
+        <v>28</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
       <c r="L85" t="s">
         <v>28</v>
       </c>
@@ -5998,7 +6502,7 @@
         <v>7</v>
       </c>
       <c r="U85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V85">
         <v>7</v>
@@ -6030,11 +6534,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H86">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I86" t="s">
         <v>15</v>
       </c>
+      <c r="J86" t="s">
+        <v>28</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
       <c r="L86" t="s">
         <v>28</v>
       </c>
@@ -6063,7 +6573,7 @@
         <v>7</v>
       </c>
       <c r="U86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V86">
         <v>7</v>
@@ -6095,10 +6605,16 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H87">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I87" t="s">
         <v>15</v>
+      </c>
+      <c r="J87" t="s">
+        <v>28</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
       </c>
       <c r="L87" t="s">
         <v>28</v>
@@ -6160,10 +6676,16 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H88">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="s">
         <v>15</v>
+      </c>
+      <c r="J88" t="s">
+        <v>31</v>
+      </c>
+      <c r="K88">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L88" t="s">
         <v>32</v>
@@ -6225,11 +6747,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H89">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I89" t="s">
         <v>15</v>
       </c>
+      <c r="J89" t="s">
+        <v>28</v>
+      </c>
+      <c r="K89">
+        <v>1</v>
+      </c>
       <c r="L89" t="s">
         <v>28</v>
       </c>
@@ -6258,7 +6786,7 @@
         <v>7</v>
       </c>
       <c r="U89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V89">
         <v>7</v>
@@ -6290,11 +6818,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H90">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I90" t="s">
         <v>15</v>
       </c>
+      <c r="J90" t="s">
+        <v>28</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
       <c r="L90" t="s">
         <v>28</v>
       </c>
@@ -6323,7 +6857,7 @@
         <v>7</v>
       </c>
       <c r="U90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V90">
         <v>7</v>
@@ -6355,11 +6889,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H91">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I91" t="s">
         <v>15</v>
       </c>
+      <c r="J91" t="s">
+        <v>28</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
       <c r="L91" t="s">
         <v>28</v>
       </c>
@@ -6388,7 +6928,7 @@
         <v>7</v>
       </c>
       <c r="U91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V91">
         <v>7</v>
@@ -6420,10 +6960,16 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H92">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I92" t="s">
         <v>15</v>
+      </c>
+      <c r="J92" t="s">
+        <v>26</v>
+      </c>
+      <c r="K92">
+        <v>0.7142857142857143</v>
       </c>
       <c r="L92" t="s">
         <v>28</v>
@@ -6485,11 +7031,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H93">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I93" t="s">
         <v>15</v>
       </c>
+      <c r="J93" t="s">
+        <v>28</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
+      </c>
       <c r="L93" t="s">
         <v>28</v>
       </c>
@@ -6518,7 +7070,7 @@
         <v>7</v>
       </c>
       <c r="U93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V93">
         <v>7</v>
@@ -6550,10 +7102,16 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H94">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I94" t="s">
         <v>15</v>
+      </c>
+      <c r="J94" t="s">
+        <v>31</v>
+      </c>
+      <c r="K94">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L94" t="s">
         <v>31</v>
@@ -6615,10 +7173,16 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H95">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I95" t="s">
         <v>15</v>
+      </c>
+      <c r="J95" t="s">
+        <v>28</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
       </c>
       <c r="L95" t="s">
         <v>33</v>
@@ -6680,11 +7244,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H96">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I96" t="s">
         <v>15</v>
       </c>
+      <c r="J96" t="s">
+        <v>28</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
       <c r="L96" t="s">
         <v>28</v>
       </c>
@@ -6713,7 +7283,7 @@
         <v>7</v>
       </c>
       <c r="U96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V96">
         <v>7</v>
@@ -6745,10 +7315,16 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H97">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I97" t="s">
         <v>15</v>
+      </c>
+      <c r="J97" t="s">
+        <v>31</v>
+      </c>
+      <c r="K97">
+        <v>0.1428571428571428</v>
       </c>
       <c r="L97" t="s">
         <v>33</v>
@@ -6810,11 +7386,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H98">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I98" t="s">
         <v>15</v>
       </c>
+      <c r="J98" t="s">
+        <v>28</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
       <c r="L98" t="s">
         <v>28</v>
       </c>
@@ -6843,7 +7425,7 @@
         <v>7</v>
       </c>
       <c r="U98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V98">
         <v>7</v>
@@ -6875,11 +7457,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H99">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I99" t="s">
         <v>15</v>
       </c>
+      <c r="J99" t="s">
+        <v>28</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
       <c r="L99" t="s">
         <v>28</v>
       </c>
@@ -6908,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="U99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V99">
         <v>7</v>
@@ -6940,11 +7528,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H100">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I100" t="s">
         <v>15</v>
       </c>
+      <c r="J100" t="s">
+        <v>28</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
       <c r="L100" t="s">
         <v>28</v>
       </c>
@@ -6973,7 +7567,7 @@
         <v>7</v>
       </c>
       <c r="U100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V100">
         <v>7</v>
@@ -7005,11 +7599,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H101">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I101" t="s">
         <v>15</v>
       </c>
+      <c r="J101" t="s">
+        <v>28</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
       <c r="L101" t="s">
         <v>28</v>
       </c>
@@ -7038,7 +7638,7 @@
         <v>7</v>
       </c>
       <c r="U101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V101">
         <v>7</v>
@@ -7070,11 +7670,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H102">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I102" t="s">
         <v>15</v>
       </c>
+      <c r="J102" t="s">
+        <v>28</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
       <c r="L102" t="s">
         <v>28</v>
       </c>
@@ -7103,7 +7709,7 @@
         <v>7</v>
       </c>
       <c r="U102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V102">
         <v>7</v>
@@ -7135,10 +7741,16 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H103">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="s">
         <v>15</v>
+      </c>
+      <c r="J103" t="s">
+        <v>28</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
       </c>
       <c r="L103" t="s">
         <v>28</v>
@@ -7200,11 +7812,17 @@
         <v>1.213154953565973</v>
       </c>
       <c r="H104">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I104" t="s">
         <v>15</v>
       </c>
+      <c r="J104" t="s">
+        <v>28</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
       <c r="L104" t="s">
         <v>28</v>
       </c>
@@ -7233,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V104">
         <v>7</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_glass.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_glass.xlsx
@@ -31,13 +31,16 @@
     <t>k</t>
   </si>
   <si>
-    <t>umbral_densidad</t>
+    <t>radio_percentil_distancias</t>
   </si>
   <si>
-    <t>umbral_riesgo</t>
+    <t>radio_percentil_riesgos</t>
   </si>
   <si>
     <t>umbral_entropia</t>
+  </si>
+  <si>
+    <t>entropia</t>
   </si>
   <si>
     <t>criterio_pureza</t>
@@ -59,9 +62,6 @@
   </si>
   <si>
     <t>riesgo_valor</t>
-  </si>
-  <si>
-    <t>entropia</t>
   </si>
   <si>
     <t>pasa_pureza</t>
@@ -572,29 +572,29 @@
       <c r="H2">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I2" t="s">
-        <v>15</v>
+      <c r="I2">
+        <v>0.863120568566631</v>
       </c>
       <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>29</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P2">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -643,29 +643,29 @@
       <c r="H3">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I3" t="s">
-        <v>15</v>
+      <c r="I3">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
         <v>27</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="s">
+        <v>33</v>
       </c>
       <c r="P3">
-        <v>0.5916727785823275</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
@@ -714,29 +714,29 @@
       <c r="H4">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I4" t="s">
-        <v>15</v>
+      <c r="I4">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>32</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
+      <c r="O4" t="s">
+        <v>33</v>
       </c>
       <c r="P4">
-        <v>0.5916727785823275</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
@@ -785,26 +785,26 @@
       <c r="H5">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I5" t="s">
-        <v>15</v>
+      <c r="I5">
+        <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
         <v>29</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
+      <c r="O5" t="s">
+        <v>33</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -856,29 +856,29 @@
       <c r="H6">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I6" t="s">
-        <v>15</v>
+      <c r="I6">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" t="s">
         <v>29</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>32</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
+      <c r="O6" t="s">
+        <v>33</v>
       </c>
       <c r="P6">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -927,26 +927,26 @@
       <c r="H7">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I7" t="s">
-        <v>15</v>
+      <c r="I7">
+        <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
         <v>29</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
+      <c r="O7" t="s">
+        <v>33</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -998,29 +998,29 @@
       <c r="H8">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I8" t="s">
-        <v>15</v>
+      <c r="I8">
+        <v>0.863120568566631</v>
       </c>
       <c r="J8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" t="s">
         <v>26</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="M8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="s">
         <v>32</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P8">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1069,29 +1069,29 @@
       <c r="H9">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I9" t="s">
-        <v>15</v>
+      <c r="I9">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J9" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" t="s">
         <v>29</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>33</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>33</v>
       </c>
       <c r="P9">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1140,29 +1140,29 @@
       <c r="H10">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I10" t="s">
-        <v>15</v>
+      <c r="I10">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" t="s">
         <v>29</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L10" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="M10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
         <v>31</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P10">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1211,26 +1211,26 @@
       <c r="H11">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I11" t="s">
-        <v>15</v>
+      <c r="I11">
+        <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
         <v>29</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
+      <c r="O11" t="s">
+        <v>33</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1282,26 +1282,26 @@
       <c r="H12">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I12" t="s">
-        <v>15</v>
+      <c r="I12">
+        <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" t="s">
         <v>29</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
+      <c r="O12" t="s">
+        <v>33</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1353,29 +1353,29 @@
       <c r="H13">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I13" t="s">
-        <v>15</v>
+      <c r="I13">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" t="s">
         <v>27</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="M13" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
         <v>31</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P13">
-        <v>0.5916727785823275</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -1424,29 +1424,29 @@
       <c r="H14">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I14" t="s">
-        <v>15</v>
+      <c r="I14">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" t="s">
         <v>27</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>27</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N14" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
+      <c r="O14" t="s">
+        <v>33</v>
       </c>
       <c r="P14">
-        <v>0.5916727785823275</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
@@ -1495,29 +1495,29 @@
       <c r="H15">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I15" t="s">
-        <v>15</v>
+      <c r="I15">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J15" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" t="s">
         <v>27</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L15" t="s">
-        <v>28</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="M15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="s">
         <v>31</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P15">
-        <v>0.5916727785823275</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
@@ -1566,29 +1566,29 @@
       <c r="H16">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I16" t="s">
-        <v>15</v>
+      <c r="I16">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J16" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" t="s">
         <v>29</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L16" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
+      <c r="M16" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>33</v>
       </c>
       <c r="P16">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -1637,29 +1637,29 @@
       <c r="H17">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I17" t="s">
-        <v>15</v>
+      <c r="I17">
+        <v>0.863120568566631</v>
       </c>
       <c r="J17" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" t="s">
         <v>26</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>30</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.4285714285714285</v>
       </c>
-      <c r="N17" t="s">
-        <v>33</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
+      <c r="O17" t="s">
+        <v>33</v>
       </c>
       <c r="P17">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -1708,26 +1708,26 @@
       <c r="H18">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I18" t="s">
-        <v>15</v>
+      <c r="I18">
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18" t="s">
-        <v>33</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K18" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>33</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -1779,29 +1779,29 @@
       <c r="H19">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I19" t="s">
-        <v>15</v>
+      <c r="I19">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J19" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" t="s">
         <v>30</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L19" t="s">
-        <v>28</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19" t="s">
-        <v>33</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
+      <c r="M19" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="s">
+        <v>33</v>
       </c>
       <c r="P19">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -1850,29 +1850,29 @@
       <c r="H20">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I20" t="s">
-        <v>15</v>
+      <c r="I20">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" t="s">
         <v>27</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>32</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N20" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
+      <c r="O20" t="s">
+        <v>33</v>
       </c>
       <c r="P20">
-        <v>0.5916727785823275</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
@@ -1921,29 +1921,29 @@
       <c r="H21">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I21" t="s">
-        <v>15</v>
+      <c r="I21">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J21" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" t="s">
         <v>29</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L21" t="s">
-        <v>28</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="M21" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
         <v>31</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P21">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -1992,29 +1992,29 @@
       <c r="H22">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I22" t="s">
-        <v>15</v>
+      <c r="I22">
+        <v>0.863120568566631</v>
       </c>
       <c r="J22" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" t="s">
         <v>26</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L22" t="s">
-        <v>28</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22" t="s">
+      <c r="M22" t="s">
+        <v>28</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" t="s">
         <v>31</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P22">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -2063,29 +2063,29 @@
       <c r="H23">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I23" t="s">
-        <v>15</v>
+      <c r="I23">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" t="s">
         <v>27</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L23" t="s">
-        <v>28</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23" t="s">
-        <v>33</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
+      <c r="M23" t="s">
+        <v>28</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>33</v>
       </c>
       <c r="P23">
-        <v>0.5916727785823275</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
@@ -2134,29 +2134,29 @@
       <c r="H24">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I24" t="s">
-        <v>15</v>
+      <c r="I24">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J24" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" t="s">
         <v>27</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L24" t="s">
-        <v>28</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="M24" t="s">
+        <v>28</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" t="s">
         <v>31</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P24">
-        <v>0.5916727785823275</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
@@ -2205,29 +2205,29 @@
       <c r="H25">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I25" t="s">
-        <v>15</v>
+      <c r="I25">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J25" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" t="s">
         <v>31</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
         <v>26</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N25" t="s">
-        <v>33</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
+      <c r="O25" t="s">
+        <v>33</v>
       </c>
       <c r="P25">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
@@ -2276,26 +2276,26 @@
       <c r="H26">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I26" t="s">
-        <v>15</v>
+      <c r="I26">
+        <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>28</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26" t="s">
-        <v>28</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26" t="s">
-        <v>33</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K26" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="s">
+        <v>33</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -2347,29 +2347,29 @@
       <c r="H27">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I27" t="s">
-        <v>15</v>
+      <c r="I27">
+        <v>0.863120568566631</v>
       </c>
       <c r="J27" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" t="s">
         <v>26</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L27" t="s">
-        <v>28</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27" t="s">
+      <c r="M27" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
         <v>31</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P27">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -2418,29 +2418,29 @@
       <c r="H28">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I28" t="s">
-        <v>15</v>
+      <c r="I28">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J28" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" t="s">
         <v>31</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L28" t="s">
-        <v>28</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28" t="s">
-        <v>33</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
+      <c r="M28" t="s">
+        <v>28</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28" t="s">
+        <v>33</v>
       </c>
       <c r="P28">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
@@ -2489,26 +2489,26 @@
       <c r="H29">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I29" t="s">
-        <v>15</v>
+      <c r="I29">
+        <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>28</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29" t="s">
+        <v>33</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -2560,29 +2560,29 @@
       <c r="H30">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I30" t="s">
-        <v>15</v>
+      <c r="I30">
+        <v>0.863120568566631</v>
       </c>
       <c r="J30" t="s">
+        <v>8</v>
+      </c>
+      <c r="K30" t="s">
         <v>26</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L30" t="s">
-        <v>28</v>
-      </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
-      <c r="N30" t="s">
+      <c r="M30" t="s">
+        <v>28</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
         <v>32</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P30">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
@@ -2631,26 +2631,26 @@
       <c r="H31">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I31" t="s">
-        <v>15</v>
+      <c r="I31">
+        <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>28</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31" t="s">
-        <v>28</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-      <c r="N31" t="s">
-        <v>33</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K31" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
+        <v>33</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -2702,26 +2702,26 @@
       <c r="H32">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I32" t="s">
-        <v>15</v>
+      <c r="I32">
+        <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>28</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32" t="s">
-        <v>28</v>
-      </c>
-      <c r="M32">
-        <v>1</v>
-      </c>
-      <c r="N32" t="s">
-        <v>33</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32" t="s">
+        <v>33</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -2773,29 +2773,29 @@
       <c r="H33">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I33" t="s">
-        <v>15</v>
+      <c r="I33">
+        <v>0.863120568566631</v>
       </c>
       <c r="J33" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" t="s">
         <v>32</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L33" t="s">
+      <c r="M33" t="s">
         <v>26</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>32</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P33">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
@@ -2844,29 +2844,29 @@
       <c r="H34">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I34" t="s">
-        <v>15</v>
+      <c r="I34">
+        <v>0.863120568566631</v>
       </c>
       <c r="J34" t="s">
+        <v>8</v>
+      </c>
+      <c r="K34" t="s">
         <v>26</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L34" t="s">
-        <v>28</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34" t="s">
+      <c r="M34" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34" t="s">
         <v>31</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P34">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
@@ -2915,29 +2915,29 @@
       <c r="H35">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I35" t="s">
-        <v>15</v>
+      <c r="I35">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J35" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" t="s">
         <v>29</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L35" t="s">
-        <v>28</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-      <c r="N35" t="s">
-        <v>33</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
+      <c r="M35" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
+        <v>33</v>
       </c>
       <c r="P35">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
@@ -2986,29 +2986,29 @@
       <c r="H36">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I36" t="s">
-        <v>15</v>
+      <c r="I36">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J36" t="s">
+        <v>8</v>
+      </c>
+      <c r="K36" t="s">
         <v>31</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L36" t="s">
-        <v>28</v>
-      </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-      <c r="N36" t="s">
+      <c r="M36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36" t="s">
         <v>29</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>0.5714285714285714</v>
-      </c>
-      <c r="P36">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q36" t="b">
         <v>1</v>
@@ -3057,26 +3057,26 @@
       <c r="H37">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I37" t="s">
-        <v>15</v>
+      <c r="I37">
+        <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>28</v>
-      </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-      <c r="L37" t="s">
-        <v>28</v>
-      </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
-      <c r="N37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K37" t="s">
+        <v>28</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37" t="s">
+        <v>33</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -3128,26 +3128,26 @@
       <c r="H38">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I38" t="s">
-        <v>15</v>
+      <c r="I38">
+        <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>28</v>
-      </c>
-      <c r="K38">
-        <v>1</v>
-      </c>
-      <c r="L38" t="s">
-        <v>33</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K38" t="s">
+        <v>28</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+      <c r="M38" t="s">
+        <v>33</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>33</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -3199,26 +3199,26 @@
       <c r="H39">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I39" t="s">
-        <v>15</v>
+      <c r="I39">
+        <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>28</v>
-      </c>
-      <c r="K39">
-        <v>1</v>
-      </c>
-      <c r="L39" t="s">
-        <v>28</v>
-      </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
-      <c r="N39" t="s">
-        <v>33</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K39" t="s">
+        <v>28</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39" t="s">
+        <v>28</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39" t="s">
+        <v>33</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -3270,26 +3270,26 @@
       <c r="H40">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I40" t="s">
-        <v>15</v>
+      <c r="I40">
+        <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>28</v>
-      </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40" t="s">
-        <v>28</v>
-      </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-      <c r="N40" t="s">
-        <v>33</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K40" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40" t="s">
+        <v>33</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -3341,26 +3341,26 @@
       <c r="H41">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I41" t="s">
-        <v>15</v>
+      <c r="I41">
+        <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>28</v>
-      </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
-      <c r="L41" t="s">
-        <v>33</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>33</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K41" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41" t="s">
+        <v>33</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>33</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -3412,26 +3412,26 @@
       <c r="H42">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I42" t="s">
-        <v>15</v>
+      <c r="I42">
+        <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>28</v>
-      </c>
-      <c r="K42">
-        <v>1</v>
-      </c>
-      <c r="L42" t="s">
-        <v>28</v>
-      </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-      <c r="N42" t="s">
-        <v>33</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42" t="s">
+        <v>33</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -3483,29 +3483,29 @@
       <c r="H43">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I43" t="s">
-        <v>15</v>
+      <c r="I43">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J43" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" t="s">
         <v>30</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L43" t="s">
-        <v>28</v>
-      </c>
-      <c r="M43">
-        <v>1</v>
-      </c>
-      <c r="N43" t="s">
-        <v>33</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
+      <c r="M43" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43" t="s">
+        <v>33</v>
       </c>
       <c r="P43">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
@@ -3554,29 +3554,29 @@
       <c r="H44">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I44" t="s">
-        <v>15</v>
+      <c r="I44">
+        <v>0.863120568566631</v>
       </c>
       <c r="J44" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" t="s">
         <v>26</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L44" t="s">
+      <c r="M44" t="s">
         <v>29</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N44" t="s">
+      <c r="O44" t="s">
         <v>31</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P44">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
@@ -3625,29 +3625,29 @@
       <c r="H45">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I45" t="s">
-        <v>15</v>
+      <c r="I45">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J45" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" t="s">
         <v>30</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L45" t="s">
-        <v>28</v>
-      </c>
-      <c r="M45">
-        <v>1</v>
-      </c>
-      <c r="N45" t="s">
+      <c r="M45" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45" t="s">
         <v>29</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>0.5714285714285714</v>
-      </c>
-      <c r="P45">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
@@ -3696,29 +3696,29 @@
       <c r="H46">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I46" t="s">
-        <v>15</v>
+      <c r="I46">
+        <v>0.863120568566631</v>
       </c>
       <c r="J46" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" t="s">
         <v>26</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L46" t="s">
-        <v>28</v>
-      </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-      <c r="N46" t="s">
-        <v>33</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
+      <c r="M46" t="s">
+        <v>28</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46" t="s">
+        <v>33</v>
       </c>
       <c r="P46">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
@@ -3767,26 +3767,26 @@
       <c r="H47">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I47" t="s">
-        <v>15</v>
+      <c r="I47">
+        <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>28</v>
-      </c>
-      <c r="K47">
-        <v>1</v>
-      </c>
-      <c r="L47" t="s">
-        <v>28</v>
-      </c>
-      <c r="M47">
-        <v>1</v>
-      </c>
-      <c r="N47" t="s">
-        <v>33</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K47" t="s">
+        <v>28</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47" t="s">
+        <v>28</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47" t="s">
+        <v>33</v>
       </c>
       <c r="P47">
         <v>0</v>
@@ -3838,29 +3838,29 @@
       <c r="H48">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I48" t="s">
-        <v>15</v>
+      <c r="I48">
+        <v>0.5916727785823275</v>
       </c>
       <c r="J48" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" t="s">
         <v>27</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L48" t="s">
+      <c r="M48" t="s">
         <v>31</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N48" t="s">
-        <v>33</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
+      <c r="O48" t="s">
+        <v>33</v>
       </c>
       <c r="P48">
-        <v>0.5916727785823275</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="b">
         <v>1</v>
@@ -3909,29 +3909,29 @@
       <c r="H49">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I49" t="s">
-        <v>15</v>
+      <c r="I49">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J49" t="s">
+        <v>8</v>
+      </c>
+      <c r="K49" t="s">
         <v>30</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L49" t="s">
+      <c r="M49" t="s">
         <v>26</v>
       </c>
-      <c r="M49">
+      <c r="N49">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N49" t="s">
+      <c r="O49" t="s">
         <v>31</v>
       </c>
-      <c r="O49">
+      <c r="P49">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P49">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
@@ -3980,29 +3980,29 @@
       <c r="H50">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I50" t="s">
-        <v>15</v>
+      <c r="I50">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J50" t="s">
+        <v>8</v>
+      </c>
+      <c r="K50" t="s">
         <v>29</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L50" t="s">
-        <v>28</v>
-      </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
-      <c r="N50" t="s">
-        <v>33</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
+      <c r="M50" t="s">
+        <v>28</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50" t="s">
+        <v>33</v>
       </c>
       <c r="P50">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
@@ -4051,26 +4051,26 @@
       <c r="H51">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I51" t="s">
-        <v>15</v>
+      <c r="I51">
+        <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>28</v>
-      </c>
-      <c r="K51">
-        <v>1</v>
-      </c>
-      <c r="L51" t="s">
-        <v>28</v>
-      </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
-      <c r="N51" t="s">
-        <v>33</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K51" t="s">
+        <v>28</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51" t="s">
+        <v>28</v>
+      </c>
+      <c r="N51">
+        <v>1</v>
+      </c>
+      <c r="O51" t="s">
+        <v>33</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -4122,29 +4122,29 @@
       <c r="H52">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I52" t="s">
-        <v>15</v>
+      <c r="I52">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J52" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" t="s">
         <v>30</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L52" t="s">
-        <v>28</v>
-      </c>
-      <c r="M52">
-        <v>1</v>
-      </c>
-      <c r="N52" t="s">
-        <v>33</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
+      <c r="M52" t="s">
+        <v>28</v>
+      </c>
+      <c r="N52">
+        <v>1</v>
+      </c>
+      <c r="O52" t="s">
+        <v>33</v>
       </c>
       <c r="P52">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
@@ -4193,29 +4193,29 @@
       <c r="H53">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I53" t="s">
-        <v>15</v>
+      <c r="I53">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J53" t="s">
+        <v>8</v>
+      </c>
+      <c r="K53" t="s">
         <v>30</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L53" t="s">
-        <v>28</v>
-      </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-      <c r="N53" t="s">
-        <v>33</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
+      <c r="M53" t="s">
+        <v>28</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53" t="s">
+        <v>33</v>
       </c>
       <c r="P53">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="b">
         <v>0</v>
@@ -4264,29 +4264,29 @@
       <c r="H54">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I54" t="s">
-        <v>15</v>
+      <c r="I54">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J54" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" t="s">
         <v>30</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L54" t="s">
-        <v>28</v>
-      </c>
-      <c r="M54">
-        <v>1</v>
-      </c>
-      <c r="N54" t="s">
-        <v>33</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
+      <c r="M54" t="s">
+        <v>28</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54" t="s">
+        <v>33</v>
       </c>
       <c r="P54">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
@@ -4335,26 +4335,26 @@
       <c r="H55">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I55" t="s">
-        <v>15</v>
+      <c r="I55">
+        <v>0</v>
       </c>
       <c r="J55" t="s">
-        <v>28</v>
-      </c>
-      <c r="K55">
-        <v>1</v>
-      </c>
-      <c r="L55" t="s">
-        <v>28</v>
-      </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
-      <c r="N55" t="s">
-        <v>33</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K55" t="s">
+        <v>28</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55" t="s">
+        <v>28</v>
+      </c>
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="O55" t="s">
+        <v>33</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -4406,29 +4406,29 @@
       <c r="H56">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I56" t="s">
-        <v>15</v>
+      <c r="I56">
+        <v>0.863120568566631</v>
       </c>
       <c r="J56" t="s">
+        <v>8</v>
+      </c>
+      <c r="K56" t="s">
         <v>26</v>
       </c>
-      <c r="K56">
+      <c r="L56">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L56" t="s">
+      <c r="M56" t="s">
         <v>32</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N56" t="s">
-        <v>33</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
+      <c r="O56" t="s">
+        <v>33</v>
       </c>
       <c r="P56">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="b">
         <v>0</v>
@@ -4477,29 +4477,29 @@
       <c r="H57">
         <v>0.5916727785823275</v>
       </c>
-      <c r="I57" t="s">
-        <v>15</v>
+      <c r="I57">
+        <v>0.863120568566631</v>
       </c>
       <c r="J57" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" t="s">
         <v>26</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L57" t="s">
+      <c r="M57" t="s">
         <v>26</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N57" t="s">
+      <c r="O57" t="s">
         <v>31</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P57">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
@@ -4548,29 +4548,29 @@
       <c r="H58">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I58" t="s">
-        <v>15</v>
+      <c r="I58">
+        <v>0.863120568566631</v>
       </c>
       <c r="J58" t="s">
+        <v>8</v>
+      </c>
+      <c r="K58" t="s">
         <v>32</v>
       </c>
-      <c r="K58">
+      <c r="L58">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L58" t="s">
-        <v>28</v>
-      </c>
-      <c r="M58">
-        <v>1</v>
-      </c>
-      <c r="N58" t="s">
+      <c r="M58" t="s">
+        <v>28</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58" t="s">
         <v>31</v>
       </c>
-      <c r="O58">
+      <c r="P58">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P58">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q58" t="b">
         <v>0</v>
@@ -4619,29 +4619,29 @@
       <c r="H59">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I59" t="s">
-        <v>15</v>
+      <c r="I59">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J59" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" t="s">
         <v>31</v>
       </c>
-      <c r="K59">
+      <c r="L59">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L59" t="s">
-        <v>28</v>
-      </c>
-      <c r="M59">
-        <v>1</v>
-      </c>
-      <c r="N59" t="s">
+      <c r="M59" t="s">
+        <v>28</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+      <c r="O59" t="s">
         <v>27</v>
       </c>
-      <c r="O59">
+      <c r="P59">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P59">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q59" t="b">
         <v>1</v>
@@ -4690,26 +4690,26 @@
       <c r="H60">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I60" t="s">
-        <v>15</v>
+      <c r="I60">
+        <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>33</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="L60" t="s">
-        <v>33</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60" t="s">
-        <v>33</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K60" t="s">
+        <v>33</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
+        <v>33</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>33</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -4761,29 +4761,29 @@
       <c r="H61">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I61" t="s">
-        <v>15</v>
+      <c r="I61">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J61" t="s">
+        <v>8</v>
+      </c>
+      <c r="K61" t="s">
         <v>31</v>
       </c>
-      <c r="K61">
+      <c r="L61">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L61" t="s">
+      <c r="M61" t="s">
         <v>26</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N61" t="s">
+      <c r="O61" t="s">
         <v>32</v>
       </c>
-      <c r="O61">
+      <c r="P61">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P61">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q61" t="b">
         <v>1</v>
@@ -4832,29 +4832,29 @@
       <c r="H62">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I62" t="s">
-        <v>15</v>
+      <c r="I62">
+        <v>0.863120568566631</v>
       </c>
       <c r="J62" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" t="s">
         <v>32</v>
       </c>
-      <c r="K62">
+      <c r="L62">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>27</v>
       </c>
-      <c r="M62">
+      <c r="N62">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N62" t="s">
-        <v>33</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
+      <c r="O62" t="s">
+        <v>33</v>
       </c>
       <c r="P62">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
@@ -4903,26 +4903,26 @@
       <c r="H63">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I63" t="s">
-        <v>15</v>
+      <c r="I63">
+        <v>0</v>
       </c>
       <c r="J63" t="s">
-        <v>33</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63" t="s">
+        <v>8</v>
+      </c>
+      <c r="K63" t="s">
+        <v>33</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="s">
         <v>26</v>
       </c>
-      <c r="M63">
+      <c r="N63">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N63" t="s">
-        <v>33</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
+      <c r="O63" t="s">
+        <v>33</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -4974,29 +4974,29 @@
       <c r="H64">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I64" t="s">
-        <v>15</v>
+      <c r="I64">
+        <v>0.863120568566631</v>
       </c>
       <c r="J64" t="s">
+        <v>8</v>
+      </c>
+      <c r="K64" t="s">
         <v>32</v>
       </c>
-      <c r="K64">
+      <c r="L64">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L64" t="s">
-        <v>28</v>
-      </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
-      <c r="N64" t="s">
+      <c r="M64" t="s">
+        <v>28</v>
+      </c>
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="s">
         <v>26</v>
       </c>
-      <c r="O64">
+      <c r="P64">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="P64">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
@@ -5045,29 +5045,29 @@
       <c r="H65">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I65" t="s">
-        <v>15</v>
+      <c r="I65">
+        <v>0.863120568566631</v>
       </c>
       <c r="J65" t="s">
+        <v>8</v>
+      </c>
+      <c r="K65" t="s">
         <v>32</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L65" t="s">
-        <v>28</v>
-      </c>
-      <c r="M65">
-        <v>1</v>
-      </c>
-      <c r="N65" t="s">
+      <c r="M65" t="s">
+        <v>28</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
+      <c r="O65" t="s">
         <v>31</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P65">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
@@ -5116,29 +5116,29 @@
       <c r="H66">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I66" t="s">
-        <v>15</v>
+      <c r="I66">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J66" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" t="s">
         <v>31</v>
       </c>
-      <c r="K66">
+      <c r="L66">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L66" t="s">
-        <v>28</v>
-      </c>
-      <c r="M66">
-        <v>1</v>
-      </c>
-      <c r="N66" t="s">
+      <c r="M66" t="s">
+        <v>28</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66" t="s">
         <v>27</v>
       </c>
-      <c r="O66">
+      <c r="P66">
         <v>0.8571428571428571</v>
-      </c>
-      <c r="P66">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q66" t="b">
         <v>1</v>
@@ -5187,29 +5187,29 @@
       <c r="H67">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I67" t="s">
-        <v>15</v>
+      <c r="I67">
+        <v>0</v>
       </c>
       <c r="J67" t="s">
-        <v>33</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67" t="s">
-        <v>28</v>
-      </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="N67" t="s">
-        <v>28</v>
-      </c>
-      <c r="O67">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="K67" t="s">
+        <v>33</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="s">
+        <v>28</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>28</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
@@ -5258,29 +5258,29 @@
       <c r="H68">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I68" t="s">
-        <v>15</v>
+      <c r="I68">
+        <v>0</v>
       </c>
       <c r="J68" t="s">
-        <v>33</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68" t="s">
-        <v>28</v>
-      </c>
-      <c r="M68">
-        <v>1</v>
-      </c>
-      <c r="N68" t="s">
+        <v>8</v>
+      </c>
+      <c r="K68" t="s">
+        <v>33</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="s">
+        <v>28</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
         <v>31</v>
       </c>
-      <c r="O68">
+      <c r="P68">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
@@ -5329,29 +5329,29 @@
       <c r="H69">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I69" t="s">
-        <v>15</v>
+      <c r="I69">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J69" t="s">
+        <v>8</v>
+      </c>
+      <c r="K69" t="s">
         <v>31</v>
       </c>
-      <c r="K69">
+      <c r="L69">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L69" t="s">
-        <v>33</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69" t="s">
-        <v>33</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
+      <c r="M69" t="s">
+        <v>33</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" t="s">
+        <v>33</v>
       </c>
       <c r="P69">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="b">
         <v>1</v>
@@ -5400,29 +5400,29 @@
       <c r="H70">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I70" t="s">
-        <v>15</v>
+      <c r="I70">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J70" t="s">
+        <v>8</v>
+      </c>
+      <c r="K70" t="s">
         <v>31</v>
       </c>
-      <c r="K70">
+      <c r="L70">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L70" t="s">
-        <v>28</v>
-      </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
-      <c r="N70" t="s">
+      <c r="M70" t="s">
+        <v>28</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
         <v>32</v>
       </c>
-      <c r="O70">
+      <c r="P70">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P70">
-        <v>0.5916727785823273</v>
       </c>
       <c r="Q70" t="b">
         <v>1</v>
@@ -5471,26 +5471,26 @@
       <c r="H71">
         <v>0.5916727785823273</v>
       </c>
-      <c r="I71" t="s">
-        <v>15</v>
+      <c r="I71">
+        <v>0</v>
       </c>
       <c r="J71" t="s">
-        <v>33</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71" t="s">
+        <v>8</v>
+      </c>
+      <c r="K71" t="s">
+        <v>33</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="s">
         <v>27</v>
       </c>
-      <c r="M71">
+      <c r="N71">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N71" t="s">
-        <v>33</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
+      <c r="O71" t="s">
+        <v>33</v>
       </c>
       <c r="P71">
         <v>0</v>
@@ -5542,26 +5542,26 @@
       <c r="H72">
         <v>0.863120568566631</v>
       </c>
-      <c r="I72" t="s">
-        <v>15</v>
+      <c r="I72">
+        <v>0</v>
       </c>
       <c r="J72" t="s">
-        <v>33</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" t="s">
+        <v>33</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72" t="s">
         <v>31</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N72" t="s">
-        <v>33</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
+      <c r="O72" t="s">
+        <v>33</v>
       </c>
       <c r="P72">
         <v>0</v>
@@ -5613,29 +5613,29 @@
       <c r="H73">
         <v>0.863120568566631</v>
       </c>
-      <c r="I73" t="s">
-        <v>15</v>
+      <c r="I73">
+        <v>0.863120568566631</v>
       </c>
       <c r="J73" t="s">
+        <v>8</v>
+      </c>
+      <c r="K73" t="s">
         <v>26</v>
       </c>
-      <c r="K73">
+      <c r="L73">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L73" t="s">
-        <v>28</v>
-      </c>
-      <c r="M73">
-        <v>1</v>
-      </c>
-      <c r="N73" t="s">
+      <c r="M73" t="s">
+        <v>28</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
         <v>32</v>
       </c>
-      <c r="O73">
+      <c r="P73">
         <v>0.2857142857142857</v>
-      </c>
-      <c r="P73">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q73" t="b">
         <v>1</v>
@@ -5684,29 +5684,29 @@
       <c r="H74">
         <v>0.863120568566631</v>
       </c>
-      <c r="I74" t="s">
-        <v>15</v>
+      <c r="I74">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J74" t="s">
+        <v>8</v>
+      </c>
+      <c r="K74" t="s">
         <v>30</v>
       </c>
-      <c r="K74">
+      <c r="L74">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L74" t="s">
-        <v>28</v>
-      </c>
-      <c r="M74">
-        <v>1</v>
-      </c>
-      <c r="N74" t="s">
+      <c r="M74" t="s">
+        <v>28</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74" t="s">
         <v>30</v>
       </c>
-      <c r="O74">
+      <c r="P74">
         <v>0.4285714285714285</v>
-      </c>
-      <c r="P74">
-        <v>0.9852281360342515</v>
       </c>
       <c r="Q74" t="b">
         <v>0</v>
@@ -5755,29 +5755,29 @@
       <c r="H75">
         <v>0.863120568566631</v>
       </c>
-      <c r="I75" t="s">
-        <v>15</v>
+      <c r="I75">
+        <v>0.863120568566631</v>
       </c>
       <c r="J75" t="s">
+        <v>8</v>
+      </c>
+      <c r="K75" t="s">
         <v>26</v>
       </c>
-      <c r="K75">
+      <c r="L75">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L75" t="s">
-        <v>28</v>
-      </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-      <c r="N75" t="s">
+      <c r="M75" t="s">
+        <v>28</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
         <v>31</v>
       </c>
-      <c r="O75">
+      <c r="P75">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P75">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q75" t="b">
         <v>1</v>
@@ -5826,29 +5826,29 @@
       <c r="H76">
         <v>0.863120568566631</v>
       </c>
-      <c r="I76" t="s">
-        <v>15</v>
+      <c r="I76">
+        <v>0</v>
       </c>
       <c r="J76" t="s">
-        <v>33</v>
-      </c>
-      <c r="K76">
-        <v>0</v>
-      </c>
-      <c r="L76" t="s">
-        <v>28</v>
-      </c>
-      <c r="M76">
-        <v>1</v>
-      </c>
-      <c r="N76" t="s">
-        <v>28</v>
-      </c>
-      <c r="O76">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="K76" t="s">
+        <v>33</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" t="s">
+        <v>28</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>28</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="b">
         <v>0</v>
@@ -5897,29 +5897,29 @@
       <c r="H77">
         <v>0.863120568566631</v>
       </c>
-      <c r="I77" t="s">
-        <v>15</v>
+      <c r="I77">
+        <v>0.863120568566631</v>
       </c>
       <c r="J77" t="s">
+        <v>8</v>
+      </c>
+      <c r="K77" t="s">
         <v>32</v>
       </c>
-      <c r="K77">
+      <c r="L77">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L77" t="s">
-        <v>33</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77" t="s">
-        <v>33</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
+      <c r="M77" t="s">
+        <v>33</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" t="s">
+        <v>33</v>
       </c>
       <c r="P77">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="b">
         <v>1</v>
@@ -5968,29 +5968,29 @@
       <c r="H78">
         <v>0.863120568566631</v>
       </c>
-      <c r="I78" t="s">
-        <v>15</v>
+      <c r="I78">
+        <v>0.863120568566631</v>
       </c>
       <c r="J78" t="s">
+        <v>8</v>
+      </c>
+      <c r="K78" t="s">
         <v>26</v>
       </c>
-      <c r="K78">
+      <c r="L78">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L78" t="s">
-        <v>28</v>
-      </c>
-      <c r="M78">
-        <v>1</v>
-      </c>
-      <c r="N78" t="s">
-        <v>33</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
+      <c r="M78" t="s">
+        <v>28</v>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
+      <c r="O78" t="s">
+        <v>33</v>
       </c>
       <c r="P78">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="b">
         <v>1</v>
@@ -6039,26 +6039,26 @@
       <c r="H79">
         <v>0.863120568566631</v>
       </c>
-      <c r="I79" t="s">
-        <v>15</v>
+      <c r="I79">
+        <v>0</v>
       </c>
       <c r="J79" t="s">
-        <v>33</v>
-      </c>
-      <c r="K79">
-        <v>0</v>
-      </c>
-      <c r="L79" t="s">
+        <v>8</v>
+      </c>
+      <c r="K79" t="s">
+        <v>33</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79" t="s">
         <v>27</v>
       </c>
-      <c r="M79">
+      <c r="N79">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N79" t="s">
-        <v>33</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
+      <c r="O79" t="s">
+        <v>33</v>
       </c>
       <c r="P79">
         <v>0</v>
@@ -6110,29 +6110,29 @@
       <c r="H80">
         <v>0.863120568566631</v>
       </c>
-      <c r="I80" t="s">
-        <v>15</v>
+      <c r="I80">
+        <v>0.9852281360342515</v>
       </c>
       <c r="J80" t="s">
+        <v>8</v>
+      </c>
+      <c r="K80" t="s">
         <v>30</v>
       </c>
-      <c r="K80">
+      <c r="L80">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L80" t="s">
-        <v>28</v>
-      </c>
-      <c r="M80">
-        <v>1</v>
-      </c>
-      <c r="N80" t="s">
-        <v>33</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
+      <c r="M80" t="s">
+        <v>28</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80" t="s">
+        <v>33</v>
       </c>
       <c r="P80">
-        <v>0.9852281360342515</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
@@ -6181,29 +6181,29 @@
       <c r="H81">
         <v>0.863120568566631</v>
       </c>
-      <c r="I81" t="s">
-        <v>15</v>
+      <c r="I81">
+        <v>0.863120568566631</v>
       </c>
       <c r="J81" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" t="s">
         <v>32</v>
       </c>
-      <c r="K81">
+      <c r="L81">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L81" t="s">
-        <v>28</v>
-      </c>
-      <c r="M81">
-        <v>1</v>
-      </c>
-      <c r="N81" t="s">
+      <c r="M81" t="s">
+        <v>28</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81" t="s">
         <v>31</v>
       </c>
-      <c r="O81">
+      <c r="P81">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P81">
-        <v>0.863120568566631</v>
       </c>
       <c r="Q81" t="b">
         <v>1</v>
@@ -6252,26 +6252,26 @@
       <c r="H82">
         <v>0</v>
       </c>
-      <c r="I82" t="s">
-        <v>15</v>
+      <c r="I82">
+        <v>0</v>
       </c>
       <c r="J82" t="s">
-        <v>33</v>
-      </c>
-      <c r="K82">
-        <v>0</v>
-      </c>
-      <c r="L82" t="s">
-        <v>33</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82" t="s">
-        <v>33</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K82" t="s">
+        <v>33</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82" t="s">
+        <v>33</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82" t="s">
+        <v>33</v>
       </c>
       <c r="P82">
         <v>0</v>
@@ -6323,29 +6323,29 @@
       <c r="H83">
         <v>0</v>
       </c>
-      <c r="I83" t="s">
-        <v>15</v>
+      <c r="I83">
+        <v>0</v>
       </c>
       <c r="J83" t="s">
-        <v>33</v>
-      </c>
-      <c r="K83">
-        <v>0</v>
-      </c>
-      <c r="L83" t="s">
-        <v>28</v>
-      </c>
-      <c r="M83">
-        <v>1</v>
-      </c>
-      <c r="N83" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" t="s">
+        <v>33</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83" t="s">
+        <v>28</v>
+      </c>
+      <c r="N83">
+        <v>1</v>
+      </c>
+      <c r="O83" t="s">
         <v>31</v>
       </c>
-      <c r="O83">
+      <c r="P83">
         <v>0.1428571428571428</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
       </c>
       <c r="Q83" t="b">
         <v>0</v>
@@ -6394,26 +6394,26 @@
       <c r="H84">
         <v>0</v>
       </c>
-      <c r="I84" t="s">
-        <v>15</v>
+      <c r="I84">
+        <v>0</v>
       </c>
       <c r="J84" t="s">
-        <v>28</v>
-      </c>
-      <c r="K84">
-        <v>1</v>
-      </c>
-      <c r="L84" t="s">
-        <v>28</v>
-      </c>
-      <c r="M84">
-        <v>1</v>
-      </c>
-      <c r="N84" t="s">
-        <v>33</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K84" t="s">
+        <v>28</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84" t="s">
+        <v>28</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84" t="s">
+        <v>33</v>
       </c>
       <c r="P84">
         <v>0</v>
@@ -6465,26 +6465,26 @@
       <c r="H85">
         <v>0</v>
       </c>
-      <c r="I85" t="s">
-        <v>15</v>
+      <c r="I85">
+        <v>0</v>
       </c>
       <c r="J85" t="s">
-        <v>28</v>
-      </c>
-      <c r="K85">
-        <v>1</v>
-      </c>
-      <c r="L85" t="s">
-        <v>28</v>
-      </c>
-      <c r="M85">
-        <v>1</v>
-      </c>
-      <c r="N85" t="s">
-        <v>33</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K85" t="s">
+        <v>28</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85" t="s">
+        <v>28</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85" t="s">
+        <v>33</v>
       </c>
       <c r="P85">
         <v>0</v>
@@ -6536,26 +6536,26 @@
       <c r="H86">
         <v>0</v>
       </c>
-      <c r="I86" t="s">
-        <v>15</v>
+      <c r="I86">
+        <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>28</v>
-      </c>
-      <c r="K86">
-        <v>1</v>
-      </c>
-      <c r="L86" t="s">
-        <v>28</v>
-      </c>
-      <c r="M86">
-        <v>1</v>
-      </c>
-      <c r="N86" t="s">
-        <v>33</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K86" t="s">
+        <v>28</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86" t="s">
+        <v>28</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" t="s">
+        <v>33</v>
       </c>
       <c r="P86">
         <v>0</v>
@@ -6607,26 +6607,26 @@
       <c r="H87">
         <v>0</v>
       </c>
-      <c r="I87" t="s">
-        <v>15</v>
+      <c r="I87">
+        <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>28</v>
-      </c>
-      <c r="K87">
-        <v>1</v>
-      </c>
-      <c r="L87" t="s">
-        <v>28</v>
-      </c>
-      <c r="M87">
-        <v>1</v>
-      </c>
-      <c r="N87" t="s">
-        <v>33</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K87" t="s">
+        <v>28</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87" t="s">
+        <v>28</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87" t="s">
+        <v>33</v>
       </c>
       <c r="P87">
         <v>0</v>
@@ -6678,29 +6678,29 @@
       <c r="H88">
         <v>0</v>
       </c>
-      <c r="I88" t="s">
-        <v>15</v>
+      <c r="I88">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J88" t="s">
+        <v>8</v>
+      </c>
+      <c r="K88" t="s">
         <v>31</v>
       </c>
-      <c r="K88">
+      <c r="L88">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L88" t="s">
+      <c r="M88" t="s">
         <v>32</v>
       </c>
-      <c r="M88">
+      <c r="N88">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N88" t="s">
-        <v>33</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
+      <c r="O88" t="s">
+        <v>33</v>
       </c>
       <c r="P88">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
@@ -6749,26 +6749,26 @@
       <c r="H89">
         <v>0</v>
       </c>
-      <c r="I89" t="s">
-        <v>15</v>
+      <c r="I89">
+        <v>0</v>
       </c>
       <c r="J89" t="s">
-        <v>28</v>
-      </c>
-      <c r="K89">
-        <v>1</v>
-      </c>
-      <c r="L89" t="s">
-        <v>28</v>
-      </c>
-      <c r="M89">
-        <v>1</v>
-      </c>
-      <c r="N89" t="s">
-        <v>33</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K89" t="s">
+        <v>28</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89" t="s">
+        <v>28</v>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
+      <c r="O89" t="s">
+        <v>33</v>
       </c>
       <c r="P89">
         <v>0</v>
@@ -6820,26 +6820,26 @@
       <c r="H90">
         <v>0</v>
       </c>
-      <c r="I90" t="s">
-        <v>15</v>
+      <c r="I90">
+        <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>28</v>
-      </c>
-      <c r="K90">
-        <v>1</v>
-      </c>
-      <c r="L90" t="s">
-        <v>28</v>
-      </c>
-      <c r="M90">
-        <v>1</v>
-      </c>
-      <c r="N90" t="s">
-        <v>33</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K90" t="s">
+        <v>28</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90" t="s">
+        <v>28</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>33</v>
       </c>
       <c r="P90">
         <v>0</v>
@@ -6891,26 +6891,26 @@
       <c r="H91">
         <v>0</v>
       </c>
-      <c r="I91" t="s">
-        <v>15</v>
+      <c r="I91">
+        <v>0</v>
       </c>
       <c r="J91" t="s">
-        <v>28</v>
-      </c>
-      <c r="K91">
-        <v>1</v>
-      </c>
-      <c r="L91" t="s">
-        <v>28</v>
-      </c>
-      <c r="M91">
-        <v>1</v>
-      </c>
-      <c r="N91" t="s">
-        <v>33</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K91" t="s">
+        <v>28</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91" t="s">
+        <v>28</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91" t="s">
+        <v>33</v>
       </c>
       <c r="P91">
         <v>0</v>
@@ -6962,29 +6962,29 @@
       <c r="H92">
         <v>0</v>
       </c>
-      <c r="I92" t="s">
-        <v>15</v>
+      <c r="I92">
+        <v>0.863120568566631</v>
       </c>
       <c r="J92" t="s">
+        <v>8</v>
+      </c>
+      <c r="K92" t="s">
         <v>26</v>
       </c>
-      <c r="K92">
+      <c r="L92">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L92" t="s">
-        <v>28</v>
-      </c>
-      <c r="M92">
-        <v>1</v>
-      </c>
-      <c r="N92" t="s">
-        <v>33</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
+      <c r="M92" t="s">
+        <v>28</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
+        <v>33</v>
       </c>
       <c r="P92">
-        <v>0.863120568566631</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
@@ -7033,26 +7033,26 @@
       <c r="H93">
         <v>0</v>
       </c>
-      <c r="I93" t="s">
-        <v>15</v>
+      <c r="I93">
+        <v>0</v>
       </c>
       <c r="J93" t="s">
-        <v>28</v>
-      </c>
-      <c r="K93">
-        <v>1</v>
-      </c>
-      <c r="L93" t="s">
-        <v>28</v>
-      </c>
-      <c r="M93">
-        <v>1</v>
-      </c>
-      <c r="N93" t="s">
-        <v>33</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K93" t="s">
+        <v>28</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93" t="s">
+        <v>28</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="O93" t="s">
+        <v>33</v>
       </c>
       <c r="P93">
         <v>0</v>
@@ -7104,29 +7104,29 @@
       <c r="H94">
         <v>0</v>
       </c>
-      <c r="I94" t="s">
-        <v>15</v>
+      <c r="I94">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J94" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" t="s">
         <v>31</v>
       </c>
-      <c r="K94">
+      <c r="L94">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L94" t="s">
+      <c r="M94" t="s">
         <v>31</v>
       </c>
-      <c r="M94">
+      <c r="N94">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N94" t="s">
-        <v>33</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
+      <c r="O94" t="s">
+        <v>33</v>
       </c>
       <c r="P94">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="b">
         <v>0</v>
@@ -7175,26 +7175,26 @@
       <c r="H95">
         <v>0</v>
       </c>
-      <c r="I95" t="s">
-        <v>15</v>
+      <c r="I95">
+        <v>0</v>
       </c>
       <c r="J95" t="s">
-        <v>28</v>
-      </c>
-      <c r="K95">
-        <v>1</v>
-      </c>
-      <c r="L95" t="s">
-        <v>33</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95" t="s">
-        <v>33</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K95" t="s">
+        <v>28</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95" t="s">
+        <v>33</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" t="s">
+        <v>33</v>
       </c>
       <c r="P95">
         <v>0</v>
@@ -7246,26 +7246,26 @@
       <c r="H96">
         <v>0</v>
       </c>
-      <c r="I96" t="s">
-        <v>15</v>
+      <c r="I96">
+        <v>0</v>
       </c>
       <c r="J96" t="s">
-        <v>28</v>
-      </c>
-      <c r="K96">
-        <v>1</v>
-      </c>
-      <c r="L96" t="s">
-        <v>28</v>
-      </c>
-      <c r="M96">
-        <v>1</v>
-      </c>
-      <c r="N96" t="s">
-        <v>33</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K96" t="s">
+        <v>28</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96" t="s">
+        <v>28</v>
+      </c>
+      <c r="N96">
+        <v>1</v>
+      </c>
+      <c r="O96" t="s">
+        <v>33</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -7317,29 +7317,29 @@
       <c r="H97">
         <v>0</v>
       </c>
-      <c r="I97" t="s">
-        <v>15</v>
+      <c r="I97">
+        <v>0.5916727785823273</v>
       </c>
       <c r="J97" t="s">
+        <v>8</v>
+      </c>
+      <c r="K97" t="s">
         <v>31</v>
       </c>
-      <c r="K97">
+      <c r="L97">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L97" t="s">
-        <v>33</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97" t="s">
-        <v>33</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
+      <c r="M97" t="s">
+        <v>33</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
+        <v>33</v>
       </c>
       <c r="P97">
-        <v>0.5916727785823273</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="b">
         <v>0</v>
@@ -7388,26 +7388,26 @@
       <c r="H98">
         <v>0</v>
       </c>
-      <c r="I98" t="s">
-        <v>15</v>
+      <c r="I98">
+        <v>0</v>
       </c>
       <c r="J98" t="s">
-        <v>28</v>
-      </c>
-      <c r="K98">
-        <v>1</v>
-      </c>
-      <c r="L98" t="s">
-        <v>28</v>
-      </c>
-      <c r="M98">
-        <v>1</v>
-      </c>
-      <c r="N98" t="s">
-        <v>33</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K98" t="s">
+        <v>28</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98" t="s">
+        <v>28</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="s">
+        <v>33</v>
       </c>
       <c r="P98">
         <v>0</v>
@@ -7459,26 +7459,26 @@
       <c r="H99">
         <v>0</v>
       </c>
-      <c r="I99" t="s">
-        <v>15</v>
+      <c r="I99">
+        <v>0</v>
       </c>
       <c r="J99" t="s">
-        <v>28</v>
-      </c>
-      <c r="K99">
-        <v>1</v>
-      </c>
-      <c r="L99" t="s">
-        <v>28</v>
-      </c>
-      <c r="M99">
-        <v>1</v>
-      </c>
-      <c r="N99" t="s">
-        <v>33</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K99" t="s">
+        <v>28</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99" t="s">
+        <v>28</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="s">
+        <v>33</v>
       </c>
       <c r="P99">
         <v>0</v>
@@ -7530,26 +7530,26 @@
       <c r="H100">
         <v>0</v>
       </c>
-      <c r="I100" t="s">
-        <v>15</v>
+      <c r="I100">
+        <v>0</v>
       </c>
       <c r="J100" t="s">
-        <v>28</v>
-      </c>
-      <c r="K100">
-        <v>1</v>
-      </c>
-      <c r="L100" t="s">
-        <v>28</v>
-      </c>
-      <c r="M100">
-        <v>1</v>
-      </c>
-      <c r="N100" t="s">
-        <v>33</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K100" t="s">
+        <v>28</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100" t="s">
+        <v>28</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100" t="s">
+        <v>33</v>
       </c>
       <c r="P100">
         <v>0</v>
@@ -7601,26 +7601,26 @@
       <c r="H101">
         <v>0</v>
       </c>
-      <c r="I101" t="s">
-        <v>15</v>
+      <c r="I101">
+        <v>0</v>
       </c>
       <c r="J101" t="s">
-        <v>28</v>
-      </c>
-      <c r="K101">
-        <v>1</v>
-      </c>
-      <c r="L101" t="s">
-        <v>28</v>
-      </c>
-      <c r="M101">
-        <v>1</v>
-      </c>
-      <c r="N101" t="s">
-        <v>33</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K101" t="s">
+        <v>28</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101" t="s">
+        <v>28</v>
+      </c>
+      <c r="N101">
+        <v>1</v>
+      </c>
+      <c r="O101" t="s">
+        <v>33</v>
       </c>
       <c r="P101">
         <v>0</v>
@@ -7672,26 +7672,26 @@
       <c r="H102">
         <v>0</v>
       </c>
-      <c r="I102" t="s">
-        <v>15</v>
+      <c r="I102">
+        <v>0</v>
       </c>
       <c r="J102" t="s">
-        <v>28</v>
-      </c>
-      <c r="K102">
-        <v>1</v>
-      </c>
-      <c r="L102" t="s">
-        <v>28</v>
-      </c>
-      <c r="M102">
-        <v>1</v>
-      </c>
-      <c r="N102" t="s">
-        <v>33</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K102" t="s">
+        <v>28</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102" t="s">
+        <v>28</v>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+      <c r="O102" t="s">
+        <v>33</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -7743,26 +7743,26 @@
       <c r="H103">
         <v>0</v>
       </c>
-      <c r="I103" t="s">
-        <v>15</v>
+      <c r="I103">
+        <v>0</v>
       </c>
       <c r="J103" t="s">
-        <v>28</v>
-      </c>
-      <c r="K103">
-        <v>1</v>
-      </c>
-      <c r="L103" t="s">
-        <v>28</v>
-      </c>
-      <c r="M103">
-        <v>1</v>
-      </c>
-      <c r="N103" t="s">
-        <v>33</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K103" t="s">
+        <v>28</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103" t="s">
+        <v>28</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="s">
+        <v>33</v>
       </c>
       <c r="P103">
         <v>0</v>
@@ -7814,26 +7814,26 @@
       <c r="H104">
         <v>0</v>
       </c>
-      <c r="I104" t="s">
-        <v>15</v>
+      <c r="I104">
+        <v>0</v>
       </c>
       <c r="J104" t="s">
-        <v>28</v>
-      </c>
-      <c r="K104">
-        <v>1</v>
-      </c>
-      <c r="L104" t="s">
-        <v>28</v>
-      </c>
-      <c r="M104">
-        <v>1</v>
-      </c>
-      <c r="N104" t="s">
-        <v>33</v>
-      </c>
-      <c r="O104">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="K104" t="s">
+        <v>28</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104" t="s">
+        <v>28</v>
+      </c>
+      <c r="N104">
+        <v>1</v>
+      </c>
+      <c r="O104" t="s">
+        <v>33</v>
       </c>
       <c r="P104">
         <v>0</v>
@@ -7882,25 +7882,25 @@
       <c r="G105">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>25</v>
       </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>26</v>
       </c>
-      <c r="K105">
+      <c r="L105">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L105" t="s">
+      <c r="M105" t="s">
         <v>29</v>
       </c>
-      <c r="M105">
+      <c r="N105">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N105" t="s">
+      <c r="O105" t="s">
         <v>31</v>
       </c>
-      <c r="O105">
+      <c r="P105">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q105" t="b">
@@ -7947,25 +7947,25 @@
       <c r="G106">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>25</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>27</v>
       </c>
-      <c r="K106">
+      <c r="L106">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L106" t="s">
-        <v>28</v>
-      </c>
-      <c r="M106">
-        <v>1</v>
-      </c>
-      <c r="N106" t="s">
-        <v>33</v>
-      </c>
-      <c r="O106">
+      <c r="M106" t="s">
+        <v>28</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>33</v>
+      </c>
+      <c r="P106">
         <v>0</v>
       </c>
       <c r="Q106" t="b">
@@ -8012,25 +8012,25 @@
       <c r="G107">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
         <v>25</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>27</v>
       </c>
-      <c r="K107">
+      <c r="L107">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L107" t="s">
+      <c r="M107" t="s">
         <v>32</v>
       </c>
-      <c r="M107">
+      <c r="N107">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N107" t="s">
-        <v>33</v>
-      </c>
-      <c r="O107">
+      <c r="O107" t="s">
+        <v>33</v>
+      </c>
+      <c r="P107">
         <v>0</v>
       </c>
       <c r="Q107" t="b">
@@ -8077,25 +8077,25 @@
       <c r="G108">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I108" t="s">
+      <c r="J108" t="s">
         <v>25</v>
       </c>
-      <c r="J108" t="s">
-        <v>28</v>
-      </c>
-      <c r="K108">
-        <v>1</v>
-      </c>
-      <c r="L108" t="s">
+      <c r="K108" t="s">
+        <v>28</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108" t="s">
         <v>29</v>
       </c>
-      <c r="M108">
+      <c r="N108">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N108" t="s">
-        <v>33</v>
-      </c>
-      <c r="O108">
+      <c r="O108" t="s">
+        <v>33</v>
+      </c>
+      <c r="P108">
         <v>0</v>
       </c>
       <c r="Q108" t="b">
@@ -8142,25 +8142,25 @@
       <c r="G109">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I109" t="s">
+      <c r="J109" t="s">
         <v>25</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>29</v>
       </c>
-      <c r="K109">
+      <c r="L109">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L109" t="s">
+      <c r="M109" t="s">
         <v>32</v>
       </c>
-      <c r="M109">
+      <c r="N109">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N109" t="s">
-        <v>33</v>
-      </c>
-      <c r="O109">
+      <c r="O109" t="s">
+        <v>33</v>
+      </c>
+      <c r="P109">
         <v>0</v>
       </c>
       <c r="Q109" t="b">
@@ -8207,25 +8207,25 @@
       <c r="G110">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I110" t="s">
+      <c r="J110" t="s">
         <v>25</v>
       </c>
-      <c r="J110" t="s">
-        <v>28</v>
-      </c>
-      <c r="K110">
-        <v>1</v>
-      </c>
-      <c r="L110" t="s">
+      <c r="K110" t="s">
+        <v>28</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110" t="s">
         <v>29</v>
       </c>
-      <c r="M110">
+      <c r="N110">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N110" t="s">
-        <v>33</v>
-      </c>
-      <c r="O110">
+      <c r="O110" t="s">
+        <v>33</v>
+      </c>
+      <c r="P110">
         <v>0</v>
       </c>
       <c r="Q110" t="b">
@@ -8272,25 +8272,25 @@
       <c r="G111">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>25</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>26</v>
       </c>
-      <c r="K111">
+      <c r="L111">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L111" t="s">
-        <v>28</v>
-      </c>
-      <c r="M111">
-        <v>1</v>
-      </c>
-      <c r="N111" t="s">
+      <c r="M111" t="s">
+        <v>28</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
         <v>32</v>
       </c>
-      <c r="O111">
+      <c r="P111">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q111" t="b">
@@ -8337,25 +8337,25 @@
       <c r="G112">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>25</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>29</v>
       </c>
-      <c r="K112">
+      <c r="L112">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L112" t="s">
-        <v>28</v>
-      </c>
-      <c r="M112">
-        <v>1</v>
-      </c>
-      <c r="N112" t="s">
-        <v>33</v>
-      </c>
-      <c r="O112">
+      <c r="M112" t="s">
+        <v>28</v>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="O112" t="s">
+        <v>33</v>
+      </c>
+      <c r="P112">
         <v>0</v>
       </c>
       <c r="Q112" t="b">
@@ -8402,25 +8402,25 @@
       <c r="G113">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>25</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>29</v>
       </c>
-      <c r="K113">
+      <c r="L113">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L113" t="s">
-        <v>28</v>
-      </c>
-      <c r="M113">
-        <v>1</v>
-      </c>
-      <c r="N113" t="s">
+      <c r="M113" t="s">
+        <v>28</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
         <v>31</v>
       </c>
-      <c r="O113">
+      <c r="P113">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q113" t="b">
@@ -8467,25 +8467,25 @@
       <c r="G114">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>25</v>
       </c>
-      <c r="J114" t="s">
-        <v>28</v>
-      </c>
-      <c r="K114">
-        <v>1</v>
-      </c>
-      <c r="L114" t="s">
+      <c r="K114" t="s">
+        <v>28</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114" t="s">
         <v>29</v>
       </c>
-      <c r="M114">
+      <c r="N114">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N114" t="s">
-        <v>33</v>
-      </c>
-      <c r="O114">
+      <c r="O114" t="s">
+        <v>33</v>
+      </c>
+      <c r="P114">
         <v>0</v>
       </c>
       <c r="Q114" t="b">
@@ -8532,25 +8532,25 @@
       <c r="G115">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>25</v>
       </c>
-      <c r="J115" t="s">
-        <v>28</v>
-      </c>
-      <c r="K115">
-        <v>1</v>
-      </c>
-      <c r="L115" t="s">
+      <c r="K115" t="s">
+        <v>28</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115" t="s">
         <v>29</v>
       </c>
-      <c r="M115">
+      <c r="N115">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N115" t="s">
-        <v>33</v>
-      </c>
-      <c r="O115">
+      <c r="O115" t="s">
+        <v>33</v>
+      </c>
+      <c r="P115">
         <v>0</v>
       </c>
       <c r="Q115" t="b">
@@ -8597,25 +8597,25 @@
       <c r="G116">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>25</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>27</v>
       </c>
-      <c r="K116">
+      <c r="L116">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L116" t="s">
-        <v>28</v>
-      </c>
-      <c r="M116">
-        <v>1</v>
-      </c>
-      <c r="N116" t="s">
+      <c r="M116" t="s">
+        <v>28</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+      <c r="O116" t="s">
         <v>31</v>
       </c>
-      <c r="O116">
+      <c r="P116">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q116" t="b">
@@ -8662,25 +8662,25 @@
       <c r="G117">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>25</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>27</v>
       </c>
-      <c r="K117">
+      <c r="L117">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L117" t="s">
+      <c r="M117" t="s">
         <v>27</v>
       </c>
-      <c r="M117">
+      <c r="N117">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N117" t="s">
-        <v>33</v>
-      </c>
-      <c r="O117">
+      <c r="O117" t="s">
+        <v>33</v>
+      </c>
+      <c r="P117">
         <v>0</v>
       </c>
       <c r="Q117" t="b">
@@ -8727,25 +8727,25 @@
       <c r="G118">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>25</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>27</v>
       </c>
-      <c r="K118">
+      <c r="L118">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L118" t="s">
-        <v>28</v>
-      </c>
-      <c r="M118">
-        <v>1</v>
-      </c>
-      <c r="N118" t="s">
+      <c r="M118" t="s">
+        <v>28</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118" t="s">
         <v>31</v>
       </c>
-      <c r="O118">
+      <c r="P118">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q118" t="b">
@@ -8792,25 +8792,25 @@
       <c r="G119">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>25</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>29</v>
       </c>
-      <c r="K119">
+      <c r="L119">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L119" t="s">
-        <v>33</v>
-      </c>
-      <c r="M119">
-        <v>0</v>
-      </c>
-      <c r="N119" t="s">
-        <v>33</v>
-      </c>
-      <c r="O119">
+      <c r="M119" t="s">
+        <v>33</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119" t="s">
+        <v>33</v>
+      </c>
+      <c r="P119">
         <v>0</v>
       </c>
       <c r="Q119" t="b">
@@ -8857,25 +8857,25 @@
       <c r="G120">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>25</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>26</v>
       </c>
-      <c r="K120">
+      <c r="L120">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L120" t="s">
+      <c r="M120" t="s">
         <v>30</v>
       </c>
-      <c r="M120">
+      <c r="N120">
         <v>0.4285714285714285</v>
       </c>
-      <c r="N120" t="s">
-        <v>33</v>
-      </c>
-      <c r="O120">
+      <c r="O120" t="s">
+        <v>33</v>
+      </c>
+      <c r="P120">
         <v>0</v>
       </c>
       <c r="Q120" t="b">
@@ -8922,25 +8922,25 @@
       <c r="G121">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J121" t="s">
         <v>25</v>
       </c>
-      <c r="J121" t="s">
-        <v>28</v>
-      </c>
-      <c r="K121">
-        <v>1</v>
-      </c>
-      <c r="L121" t="s">
-        <v>28</v>
-      </c>
-      <c r="M121">
-        <v>1</v>
-      </c>
-      <c r="N121" t="s">
-        <v>33</v>
-      </c>
-      <c r="O121">
+      <c r="K121" t="s">
+        <v>28</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121" t="s">
+        <v>28</v>
+      </c>
+      <c r="N121">
+        <v>1</v>
+      </c>
+      <c r="O121" t="s">
+        <v>33</v>
+      </c>
+      <c r="P121">
         <v>0</v>
       </c>
       <c r="Q121" t="b">
@@ -8987,25 +8987,25 @@
       <c r="G122">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I122" t="s">
+      <c r="J122" t="s">
         <v>25</v>
       </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
         <v>30</v>
       </c>
-      <c r="K122">
+      <c r="L122">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L122" t="s">
-        <v>28</v>
-      </c>
-      <c r="M122">
-        <v>1</v>
-      </c>
-      <c r="N122" t="s">
-        <v>33</v>
-      </c>
-      <c r="O122">
+      <c r="M122" t="s">
+        <v>28</v>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+      <c r="O122" t="s">
+        <v>33</v>
+      </c>
+      <c r="P122">
         <v>0</v>
       </c>
       <c r="Q122" t="b">
@@ -9052,25 +9052,25 @@
       <c r="G123">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I123" t="s">
+      <c r="J123" t="s">
         <v>25</v>
       </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>27</v>
       </c>
-      <c r="K123">
+      <c r="L123">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L123" t="s">
+      <c r="M123" t="s">
         <v>32</v>
       </c>
-      <c r="M123">
+      <c r="N123">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N123" t="s">
-        <v>33</v>
-      </c>
-      <c r="O123">
+      <c r="O123" t="s">
+        <v>33</v>
+      </c>
+      <c r="P123">
         <v>0</v>
       </c>
       <c r="Q123" t="b">
@@ -9117,25 +9117,25 @@
       <c r="G124">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I124" t="s">
+      <c r="J124" t="s">
         <v>25</v>
       </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>29</v>
       </c>
-      <c r="K124">
+      <c r="L124">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L124" t="s">
-        <v>28</v>
-      </c>
-      <c r="M124">
-        <v>1</v>
-      </c>
-      <c r="N124" t="s">
+      <c r="M124" t="s">
+        <v>28</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
         <v>31</v>
       </c>
-      <c r="O124">
+      <c r="P124">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q124" t="b">
@@ -9182,25 +9182,25 @@
       <c r="G125">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>25</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
         <v>26</v>
       </c>
-      <c r="K125">
+      <c r="L125">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L125" t="s">
-        <v>28</v>
-      </c>
-      <c r="M125">
-        <v>1</v>
-      </c>
-      <c r="N125" t="s">
+      <c r="M125" t="s">
+        <v>28</v>
+      </c>
+      <c r="N125">
+        <v>1</v>
+      </c>
+      <c r="O125" t="s">
         <v>31</v>
       </c>
-      <c r="O125">
+      <c r="P125">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q125" t="b">
@@ -9247,25 +9247,25 @@
       <c r="G126">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I126" t="s">
+      <c r="J126" t="s">
         <v>25</v>
       </c>
-      <c r="J126" t="s">
+      <c r="K126" t="s">
         <v>27</v>
       </c>
-      <c r="K126">
+      <c r="L126">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L126" t="s">
-        <v>28</v>
-      </c>
-      <c r="M126">
-        <v>1</v>
-      </c>
-      <c r="N126" t="s">
-        <v>33</v>
-      </c>
-      <c r="O126">
+      <c r="M126" t="s">
+        <v>28</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>33</v>
+      </c>
+      <c r="P126">
         <v>0</v>
       </c>
       <c r="Q126" t="b">
@@ -9312,25 +9312,25 @@
       <c r="G127">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>25</v>
       </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
         <v>27</v>
       </c>
-      <c r="K127">
+      <c r="L127">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L127" t="s">
-        <v>28</v>
-      </c>
-      <c r="M127">
-        <v>1</v>
-      </c>
-      <c r="N127" t="s">
+      <c r="M127" t="s">
+        <v>28</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
         <v>31</v>
       </c>
-      <c r="O127">
+      <c r="P127">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q127" t="b">
@@ -9377,25 +9377,25 @@
       <c r="G128">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>25</v>
       </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
         <v>31</v>
       </c>
-      <c r="K128">
+      <c r="L128">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L128" t="s">
+      <c r="M128" t="s">
         <v>26</v>
       </c>
-      <c r="M128">
+      <c r="N128">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N128" t="s">
-        <v>33</v>
-      </c>
-      <c r="O128">
+      <c r="O128" t="s">
+        <v>33</v>
+      </c>
+      <c r="P128">
         <v>0</v>
       </c>
       <c r="Q128" t="b">
@@ -9442,25 +9442,25 @@
       <c r="G129">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I129" t="s">
+      <c r="J129" t="s">
         <v>25</v>
       </c>
-      <c r="J129" t="s">
-        <v>28</v>
-      </c>
-      <c r="K129">
-        <v>1</v>
-      </c>
-      <c r="L129" t="s">
-        <v>28</v>
-      </c>
-      <c r="M129">
-        <v>1</v>
-      </c>
-      <c r="N129" t="s">
-        <v>33</v>
-      </c>
-      <c r="O129">
+      <c r="K129" t="s">
+        <v>28</v>
+      </c>
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="M129" t="s">
+        <v>28</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129" t="s">
+        <v>33</v>
+      </c>
+      <c r="P129">
         <v>0</v>
       </c>
       <c r="Q129" t="b">
@@ -9507,25 +9507,25 @@
       <c r="G130">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
         <v>25</v>
       </c>
-      <c r="J130" t="s">
+      <c r="K130" t="s">
         <v>26</v>
       </c>
-      <c r="K130">
+      <c r="L130">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L130" t="s">
-        <v>28</v>
-      </c>
-      <c r="M130">
-        <v>1</v>
-      </c>
-      <c r="N130" t="s">
+      <c r="M130" t="s">
+        <v>28</v>
+      </c>
+      <c r="N130">
+        <v>1</v>
+      </c>
+      <c r="O130" t="s">
         <v>31</v>
       </c>
-      <c r="O130">
+      <c r="P130">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q130" t="b">
@@ -9572,25 +9572,25 @@
       <c r="G131">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I131" t="s">
+      <c r="J131" t="s">
         <v>25</v>
       </c>
-      <c r="J131" t="s">
+      <c r="K131" t="s">
         <v>31</v>
       </c>
-      <c r="K131">
+      <c r="L131">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L131" t="s">
-        <v>28</v>
-      </c>
-      <c r="M131">
-        <v>1</v>
-      </c>
-      <c r="N131" t="s">
-        <v>33</v>
-      </c>
-      <c r="O131">
+      <c r="M131" t="s">
+        <v>28</v>
+      </c>
+      <c r="N131">
+        <v>1</v>
+      </c>
+      <c r="O131" t="s">
+        <v>33</v>
+      </c>
+      <c r="P131">
         <v>0</v>
       </c>
       <c r="Q131" t="b">
@@ -9637,25 +9637,25 @@
       <c r="G132">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I132" t="s">
+      <c r="J132" t="s">
         <v>25</v>
       </c>
-      <c r="J132" t="s">
-        <v>28</v>
-      </c>
-      <c r="K132">
-        <v>1</v>
-      </c>
-      <c r="L132" t="s">
-        <v>28</v>
-      </c>
-      <c r="M132">
-        <v>1</v>
-      </c>
-      <c r="N132" t="s">
-        <v>33</v>
-      </c>
-      <c r="O132">
+      <c r="K132" t="s">
+        <v>28</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132" t="s">
+        <v>28</v>
+      </c>
+      <c r="N132">
+        <v>1</v>
+      </c>
+      <c r="O132" t="s">
+        <v>33</v>
+      </c>
+      <c r="P132">
         <v>0</v>
       </c>
       <c r="Q132" t="b">
@@ -9702,25 +9702,25 @@
       <c r="G133">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I133" t="s">
+      <c r="J133" t="s">
         <v>25</v>
       </c>
-      <c r="J133" t="s">
+      <c r="K133" t="s">
         <v>26</v>
       </c>
-      <c r="K133">
+      <c r="L133">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L133" t="s">
-        <v>28</v>
-      </c>
-      <c r="M133">
-        <v>1</v>
-      </c>
-      <c r="N133" t="s">
+      <c r="M133" t="s">
+        <v>28</v>
+      </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
+      <c r="O133" t="s">
         <v>32</v>
       </c>
-      <c r="O133">
+      <c r="P133">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q133" t="b">
@@ -9767,25 +9767,25 @@
       <c r="G134">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I134" t="s">
+      <c r="J134" t="s">
         <v>25</v>
       </c>
-      <c r="J134" t="s">
-        <v>28</v>
-      </c>
-      <c r="K134">
-        <v>1</v>
-      </c>
-      <c r="L134" t="s">
-        <v>28</v>
-      </c>
-      <c r="M134">
-        <v>1</v>
-      </c>
-      <c r="N134" t="s">
-        <v>33</v>
-      </c>
-      <c r="O134">
+      <c r="K134" t="s">
+        <v>28</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134" t="s">
+        <v>28</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134" t="s">
+        <v>33</v>
+      </c>
+      <c r="P134">
         <v>0</v>
       </c>
       <c r="Q134" t="b">
@@ -9832,25 +9832,25 @@
       <c r="G135">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I135" t="s">
+      <c r="J135" t="s">
         <v>25</v>
       </c>
-      <c r="J135" t="s">
-        <v>28</v>
-      </c>
-      <c r="K135">
-        <v>1</v>
-      </c>
-      <c r="L135" t="s">
-        <v>28</v>
-      </c>
-      <c r="M135">
-        <v>1</v>
-      </c>
-      <c r="N135" t="s">
-        <v>33</v>
-      </c>
-      <c r="O135">
+      <c r="K135" t="s">
+        <v>28</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135" t="s">
+        <v>28</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>33</v>
+      </c>
+      <c r="P135">
         <v>0</v>
       </c>
       <c r="Q135" t="b">
@@ -9897,25 +9897,25 @@
       <c r="G136">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I136" t="s">
+      <c r="J136" t="s">
         <v>25</v>
       </c>
-      <c r="J136" t="s">
+      <c r="K136" t="s">
         <v>32</v>
       </c>
-      <c r="K136">
+      <c r="L136">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L136" t="s">
+      <c r="M136" t="s">
         <v>26</v>
       </c>
-      <c r="M136">
+      <c r="N136">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N136" t="s">
+      <c r="O136" t="s">
         <v>32</v>
       </c>
-      <c r="O136">
+      <c r="P136">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q136" t="b">
@@ -9962,25 +9962,25 @@
       <c r="G137">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I137" t="s">
+      <c r="J137" t="s">
         <v>25</v>
       </c>
-      <c r="J137" t="s">
+      <c r="K137" t="s">
         <v>26</v>
       </c>
-      <c r="K137">
+      <c r="L137">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L137" t="s">
-        <v>28</v>
-      </c>
-      <c r="M137">
-        <v>1</v>
-      </c>
-      <c r="N137" t="s">
+      <c r="M137" t="s">
+        <v>28</v>
+      </c>
+      <c r="N137">
+        <v>1</v>
+      </c>
+      <c r="O137" t="s">
         <v>31</v>
       </c>
-      <c r="O137">
+      <c r="P137">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q137" t="b">
@@ -10027,25 +10027,25 @@
       <c r="G138">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I138" t="s">
+      <c r="J138" t="s">
         <v>25</v>
       </c>
-      <c r="J138" t="s">
+      <c r="K138" t="s">
         <v>29</v>
       </c>
-      <c r="K138">
+      <c r="L138">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L138" t="s">
-        <v>28</v>
-      </c>
-      <c r="M138">
-        <v>1</v>
-      </c>
-      <c r="N138" t="s">
-        <v>33</v>
-      </c>
-      <c r="O138">
+      <c r="M138" t="s">
+        <v>28</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138" t="s">
+        <v>33</v>
+      </c>
+      <c r="P138">
         <v>0</v>
       </c>
       <c r="Q138" t="b">
@@ -10092,25 +10092,25 @@
       <c r="G139">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I139" t="s">
+      <c r="J139" t="s">
         <v>25</v>
       </c>
-      <c r="J139" t="s">
+      <c r="K139" t="s">
         <v>31</v>
       </c>
-      <c r="K139">
+      <c r="L139">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L139" t="s">
-        <v>28</v>
-      </c>
-      <c r="M139">
-        <v>1</v>
-      </c>
-      <c r="N139" t="s">
+      <c r="M139" t="s">
+        <v>28</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139" t="s">
         <v>29</v>
       </c>
-      <c r="O139">
+      <c r="P139">
         <v>0.5714285714285714</v>
       </c>
       <c r="Q139" t="b">
@@ -10157,25 +10157,25 @@
       <c r="G140">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I140" t="s">
+      <c r="J140" t="s">
         <v>25</v>
       </c>
-      <c r="J140" t="s">
-        <v>28</v>
-      </c>
-      <c r="K140">
-        <v>1</v>
-      </c>
-      <c r="L140" t="s">
-        <v>28</v>
-      </c>
-      <c r="M140">
-        <v>1</v>
-      </c>
-      <c r="N140" t="s">
-        <v>33</v>
-      </c>
-      <c r="O140">
+      <c r="K140" t="s">
+        <v>28</v>
+      </c>
+      <c r="L140">
+        <v>1</v>
+      </c>
+      <c r="M140" t="s">
+        <v>28</v>
+      </c>
+      <c r="N140">
+        <v>1</v>
+      </c>
+      <c r="O140" t="s">
+        <v>33</v>
+      </c>
+      <c r="P140">
         <v>0</v>
       </c>
       <c r="Q140" t="b">
@@ -10222,25 +10222,25 @@
       <c r="G141">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J141" t="s">
         <v>25</v>
       </c>
-      <c r="J141" t="s">
-        <v>28</v>
-      </c>
-      <c r="K141">
-        <v>1</v>
-      </c>
-      <c r="L141" t="s">
-        <v>33</v>
-      </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-      <c r="N141" t="s">
-        <v>33</v>
-      </c>
-      <c r="O141">
+      <c r="K141" t="s">
+        <v>28</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141" t="s">
+        <v>33</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141" t="s">
+        <v>33</v>
+      </c>
+      <c r="P141">
         <v>0</v>
       </c>
       <c r="Q141" t="b">
@@ -10287,25 +10287,25 @@
       <c r="G142">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>25</v>
       </c>
-      <c r="J142" t="s">
-        <v>28</v>
-      </c>
-      <c r="K142">
-        <v>1</v>
-      </c>
-      <c r="L142" t="s">
-        <v>28</v>
-      </c>
-      <c r="M142">
-        <v>1</v>
-      </c>
-      <c r="N142" t="s">
-        <v>33</v>
-      </c>
-      <c r="O142">
+      <c r="K142" t="s">
+        <v>28</v>
+      </c>
+      <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="M142" t="s">
+        <v>28</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+      <c r="O142" t="s">
+        <v>33</v>
+      </c>
+      <c r="P142">
         <v>0</v>
       </c>
       <c r="Q142" t="b">
@@ -10352,25 +10352,25 @@
       <c r="G143">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I143" t="s">
+      <c r="J143" t="s">
         <v>25</v>
       </c>
-      <c r="J143" t="s">
-        <v>28</v>
-      </c>
-      <c r="K143">
-        <v>1</v>
-      </c>
-      <c r="L143" t="s">
-        <v>28</v>
-      </c>
-      <c r="M143">
-        <v>1</v>
-      </c>
-      <c r="N143" t="s">
-        <v>33</v>
-      </c>
-      <c r="O143">
+      <c r="K143" t="s">
+        <v>28</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="M143" t="s">
+        <v>28</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143" t="s">
+        <v>33</v>
+      </c>
+      <c r="P143">
         <v>0</v>
       </c>
       <c r="Q143" t="b">
@@ -10417,25 +10417,25 @@
       <c r="G144">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I144" t="s">
+      <c r="J144" t="s">
         <v>25</v>
       </c>
-      <c r="J144" t="s">
-        <v>28</v>
-      </c>
-      <c r="K144">
-        <v>1</v>
-      </c>
-      <c r="L144" t="s">
-        <v>33</v>
-      </c>
-      <c r="M144">
-        <v>0</v>
-      </c>
-      <c r="N144" t="s">
-        <v>33</v>
-      </c>
-      <c r="O144">
+      <c r="K144" t="s">
+        <v>28</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+      <c r="M144" t="s">
+        <v>33</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144" t="s">
+        <v>33</v>
+      </c>
+      <c r="P144">
         <v>0</v>
       </c>
       <c r="Q144" t="b">
@@ -10482,25 +10482,25 @@
       <c r="G145">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I145" t="s">
+      <c r="J145" t="s">
         <v>25</v>
       </c>
-      <c r="J145" t="s">
-        <v>28</v>
-      </c>
-      <c r="K145">
-        <v>1</v>
-      </c>
-      <c r="L145" t="s">
-        <v>28</v>
-      </c>
-      <c r="M145">
-        <v>1</v>
-      </c>
-      <c r="N145" t="s">
-        <v>33</v>
-      </c>
-      <c r="O145">
+      <c r="K145" t="s">
+        <v>28</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145" t="s">
+        <v>28</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
+        <v>33</v>
+      </c>
+      <c r="P145">
         <v>0</v>
       </c>
       <c r="Q145" t="b">
@@ -10547,25 +10547,25 @@
       <c r="G146">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I146" t="s">
+      <c r="J146" t="s">
         <v>25</v>
       </c>
-      <c r="J146" t="s">
+      <c r="K146" t="s">
         <v>30</v>
       </c>
-      <c r="K146">
+      <c r="L146">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L146" t="s">
-        <v>28</v>
-      </c>
-      <c r="M146">
-        <v>1</v>
-      </c>
-      <c r="N146" t="s">
-        <v>33</v>
-      </c>
-      <c r="O146">
+      <c r="M146" t="s">
+        <v>28</v>
+      </c>
+      <c r="N146">
+        <v>1</v>
+      </c>
+      <c r="O146" t="s">
+        <v>33</v>
+      </c>
+      <c r="P146">
         <v>0</v>
       </c>
       <c r="Q146" t="b">
@@ -10612,25 +10612,25 @@
       <c r="G147">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I147" t="s">
+      <c r="J147" t="s">
         <v>25</v>
       </c>
-      <c r="J147" t="s">
+      <c r="K147" t="s">
         <v>26</v>
       </c>
-      <c r="K147">
+      <c r="L147">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L147" t="s">
+      <c r="M147" t="s">
         <v>29</v>
       </c>
-      <c r="M147">
+      <c r="N147">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N147" t="s">
+      <c r="O147" t="s">
         <v>31</v>
       </c>
-      <c r="O147">
+      <c r="P147">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q147" t="b">
@@ -10677,25 +10677,25 @@
       <c r="G148">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I148" t="s">
+      <c r="J148" t="s">
         <v>25</v>
       </c>
-      <c r="J148" t="s">
+      <c r="K148" t="s">
         <v>30</v>
       </c>
-      <c r="K148">
+      <c r="L148">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L148" t="s">
-        <v>28</v>
-      </c>
-      <c r="M148">
-        <v>1</v>
-      </c>
-      <c r="N148" t="s">
+      <c r="M148" t="s">
+        <v>28</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148" t="s">
         <v>29</v>
       </c>
-      <c r="O148">
+      <c r="P148">
         <v>0.5714285714285714</v>
       </c>
       <c r="Q148" t="b">
@@ -10742,25 +10742,25 @@
       <c r="G149">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I149" t="s">
+      <c r="J149" t="s">
         <v>25</v>
       </c>
-      <c r="J149" t="s">
+      <c r="K149" t="s">
         <v>26</v>
       </c>
-      <c r="K149">
+      <c r="L149">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L149" t="s">
-        <v>28</v>
-      </c>
-      <c r="M149">
-        <v>1</v>
-      </c>
-      <c r="N149" t="s">
-        <v>33</v>
-      </c>
-      <c r="O149">
+      <c r="M149" t="s">
+        <v>28</v>
+      </c>
+      <c r="N149">
+        <v>1</v>
+      </c>
+      <c r="O149" t="s">
+        <v>33</v>
+      </c>
+      <c r="P149">
         <v>0</v>
       </c>
       <c r="Q149" t="b">
@@ -10807,25 +10807,25 @@
       <c r="G150">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I150" t="s">
+      <c r="J150" t="s">
         <v>25</v>
       </c>
-      <c r="J150" t="s">
-        <v>28</v>
-      </c>
-      <c r="K150">
-        <v>1</v>
-      </c>
-      <c r="L150" t="s">
-        <v>28</v>
-      </c>
-      <c r="M150">
-        <v>1</v>
-      </c>
-      <c r="N150" t="s">
-        <v>33</v>
-      </c>
-      <c r="O150">
+      <c r="K150" t="s">
+        <v>28</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150" t="s">
+        <v>28</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
+        <v>33</v>
+      </c>
+      <c r="P150">
         <v>0</v>
       </c>
       <c r="Q150" t="b">
@@ -10872,25 +10872,25 @@
       <c r="G151">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I151" t="s">
+      <c r="J151" t="s">
         <v>25</v>
       </c>
-      <c r="J151" t="s">
+      <c r="K151" t="s">
         <v>27</v>
       </c>
-      <c r="K151">
+      <c r="L151">
         <v>0.8571428571428571</v>
       </c>
-      <c r="L151" t="s">
+      <c r="M151" t="s">
         <v>31</v>
       </c>
-      <c r="M151">
+      <c r="N151">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N151" t="s">
-        <v>33</v>
-      </c>
-      <c r="O151">
+      <c r="O151" t="s">
+        <v>33</v>
+      </c>
+      <c r="P151">
         <v>0</v>
       </c>
       <c r="Q151" t="b">
@@ -10937,25 +10937,25 @@
       <c r="G152">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I152" t="s">
+      <c r="J152" t="s">
         <v>25</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
         <v>30</v>
       </c>
-      <c r="K152">
+      <c r="L152">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L152" t="s">
+      <c r="M152" t="s">
         <v>26</v>
       </c>
-      <c r="M152">
+      <c r="N152">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N152" t="s">
+      <c r="O152" t="s">
         <v>31</v>
       </c>
-      <c r="O152">
+      <c r="P152">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q152" t="b">
@@ -11002,25 +11002,25 @@
       <c r="G153">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I153" t="s">
+      <c r="J153" t="s">
         <v>25</v>
       </c>
-      <c r="J153" t="s">
+      <c r="K153" t="s">
         <v>29</v>
       </c>
-      <c r="K153">
+      <c r="L153">
         <v>0.5714285714285714</v>
       </c>
-      <c r="L153" t="s">
-        <v>28</v>
-      </c>
-      <c r="M153">
-        <v>1</v>
-      </c>
-      <c r="N153" t="s">
-        <v>33</v>
-      </c>
-      <c r="O153">
+      <c r="M153" t="s">
+        <v>28</v>
+      </c>
+      <c r="N153">
+        <v>1</v>
+      </c>
+      <c r="O153" t="s">
+        <v>33</v>
+      </c>
+      <c r="P153">
         <v>0</v>
       </c>
       <c r="Q153" t="b">
@@ -11067,25 +11067,25 @@
       <c r="G154">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I154" t="s">
+      <c r="J154" t="s">
         <v>25</v>
       </c>
-      <c r="J154" t="s">
-        <v>28</v>
-      </c>
-      <c r="K154">
-        <v>1</v>
-      </c>
-      <c r="L154" t="s">
-        <v>28</v>
-      </c>
-      <c r="M154">
-        <v>1</v>
-      </c>
-      <c r="N154" t="s">
-        <v>33</v>
-      </c>
-      <c r="O154">
+      <c r="K154" t="s">
+        <v>28</v>
+      </c>
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="M154" t="s">
+        <v>28</v>
+      </c>
+      <c r="N154">
+        <v>1</v>
+      </c>
+      <c r="O154" t="s">
+        <v>33</v>
+      </c>
+      <c r="P154">
         <v>0</v>
       </c>
       <c r="Q154" t="b">
@@ -11132,25 +11132,25 @@
       <c r="G155">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I155" t="s">
+      <c r="J155" t="s">
         <v>25</v>
       </c>
-      <c r="J155" t="s">
+      <c r="K155" t="s">
         <v>30</v>
       </c>
-      <c r="K155">
+      <c r="L155">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L155" t="s">
-        <v>28</v>
-      </c>
-      <c r="M155">
-        <v>1</v>
-      </c>
-      <c r="N155" t="s">
-        <v>33</v>
-      </c>
-      <c r="O155">
+      <c r="M155" t="s">
+        <v>28</v>
+      </c>
+      <c r="N155">
+        <v>1</v>
+      </c>
+      <c r="O155" t="s">
+        <v>33</v>
+      </c>
+      <c r="P155">
         <v>0</v>
       </c>
       <c r="Q155" t="b">
@@ -11197,25 +11197,25 @@
       <c r="G156">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I156" t="s">
+      <c r="J156" t="s">
         <v>25</v>
       </c>
-      <c r="J156" t="s">
+      <c r="K156" t="s">
         <v>30</v>
       </c>
-      <c r="K156">
+      <c r="L156">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L156" t="s">
-        <v>28</v>
-      </c>
-      <c r="M156">
-        <v>1</v>
-      </c>
-      <c r="N156" t="s">
-        <v>33</v>
-      </c>
-      <c r="O156">
+      <c r="M156" t="s">
+        <v>28</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="O156" t="s">
+        <v>33</v>
+      </c>
+      <c r="P156">
         <v>0</v>
       </c>
       <c r="Q156" t="b">
@@ -11262,25 +11262,25 @@
       <c r="G157">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I157" t="s">
+      <c r="J157" t="s">
         <v>25</v>
       </c>
-      <c r="J157" t="s">
+      <c r="K157" t="s">
         <v>30</v>
       </c>
-      <c r="K157">
+      <c r="L157">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L157" t="s">
-        <v>28</v>
-      </c>
-      <c r="M157">
-        <v>1</v>
-      </c>
-      <c r="N157" t="s">
-        <v>33</v>
-      </c>
-      <c r="O157">
+      <c r="M157" t="s">
+        <v>28</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157" t="s">
+        <v>33</v>
+      </c>
+      <c r="P157">
         <v>0</v>
       </c>
       <c r="Q157" t="b">
@@ -11327,25 +11327,25 @@
       <c r="G158">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I158" t="s">
+      <c r="J158" t="s">
         <v>25</v>
       </c>
-      <c r="J158" t="s">
-        <v>28</v>
-      </c>
-      <c r="K158">
-        <v>1</v>
-      </c>
-      <c r="L158" t="s">
-        <v>28</v>
-      </c>
-      <c r="M158">
-        <v>1</v>
-      </c>
-      <c r="N158" t="s">
-        <v>33</v>
-      </c>
-      <c r="O158">
+      <c r="K158" t="s">
+        <v>28</v>
+      </c>
+      <c r="L158">
+        <v>1</v>
+      </c>
+      <c r="M158" t="s">
+        <v>28</v>
+      </c>
+      <c r="N158">
+        <v>1</v>
+      </c>
+      <c r="O158" t="s">
+        <v>33</v>
+      </c>
+      <c r="P158">
         <v>0</v>
       </c>
       <c r="Q158" t="b">
@@ -11392,25 +11392,25 @@
       <c r="G159">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I159" t="s">
+      <c r="J159" t="s">
         <v>25</v>
       </c>
-      <c r="J159" t="s">
+      <c r="K159" t="s">
         <v>26</v>
       </c>
-      <c r="K159">
+      <c r="L159">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L159" t="s">
+      <c r="M159" t="s">
         <v>32</v>
       </c>
-      <c r="M159">
+      <c r="N159">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N159" t="s">
-        <v>33</v>
-      </c>
-      <c r="O159">
+      <c r="O159" t="s">
+        <v>33</v>
+      </c>
+      <c r="P159">
         <v>0</v>
       </c>
       <c r="Q159" t="b">
@@ -11457,25 +11457,25 @@
       <c r="G160">
         <v>0.5817985234708472</v>
       </c>
-      <c r="I160" t="s">
+      <c r="J160" t="s">
         <v>25</v>
       </c>
-      <c r="J160" t="s">
+      <c r="K160" t="s">
         <v>26</v>
       </c>
-      <c r="K160">
+      <c r="L160">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L160" t="s">
+      <c r="M160" t="s">
         <v>26</v>
       </c>
-      <c r="M160">
+      <c r="N160">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N160" t="s">
+      <c r="O160" t="s">
         <v>31</v>
       </c>
-      <c r="O160">
+      <c r="P160">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q160" t="b">
@@ -11522,25 +11522,25 @@
       <c r="G161">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I161" t="s">
+      <c r="J161" t="s">
         <v>25</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>32</v>
       </c>
-      <c r="K161">
+      <c r="L161">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L161" t="s">
-        <v>28</v>
-      </c>
-      <c r="M161">
-        <v>1</v>
-      </c>
-      <c r="N161" t="s">
+      <c r="M161" t="s">
+        <v>28</v>
+      </c>
+      <c r="N161">
+        <v>1</v>
+      </c>
+      <c r="O161" t="s">
         <v>31</v>
       </c>
-      <c r="O161">
+      <c r="P161">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q161" t="b">
@@ -11587,25 +11587,25 @@
       <c r="G162">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I162" t="s">
+      <c r="J162" t="s">
         <v>25</v>
       </c>
-      <c r="J162" t="s">
+      <c r="K162" t="s">
         <v>31</v>
       </c>
-      <c r="K162">
+      <c r="L162">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L162" t="s">
-        <v>28</v>
-      </c>
-      <c r="M162">
-        <v>1</v>
-      </c>
-      <c r="N162" t="s">
+      <c r="M162" t="s">
+        <v>28</v>
+      </c>
+      <c r="N162">
+        <v>1</v>
+      </c>
+      <c r="O162" t="s">
         <v>27</v>
       </c>
-      <c r="O162">
+      <c r="P162">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q162" t="b">
@@ -11652,25 +11652,25 @@
       <c r="G163">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I163" t="s">
+      <c r="J163" t="s">
         <v>25</v>
       </c>
-      <c r="J163" t="s">
-        <v>33</v>
-      </c>
-      <c r="K163">
-        <v>0</v>
-      </c>
-      <c r="L163" t="s">
-        <v>33</v>
-      </c>
-      <c r="M163">
-        <v>0</v>
-      </c>
-      <c r="N163" t="s">
-        <v>33</v>
-      </c>
-      <c r="O163">
+      <c r="K163" t="s">
+        <v>33</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163" t="s">
+        <v>33</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163" t="s">
+        <v>33</v>
+      </c>
+      <c r="P163">
         <v>0</v>
       </c>
       <c r="Q163" t="b">
@@ -11717,25 +11717,25 @@
       <c r="G164">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I164" t="s">
+      <c r="J164" t="s">
         <v>25</v>
       </c>
-      <c r="J164" t="s">
+      <c r="K164" t="s">
         <v>31</v>
       </c>
-      <c r="K164">
+      <c r="L164">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L164" t="s">
+      <c r="M164" t="s">
         <v>26</v>
       </c>
-      <c r="M164">
+      <c r="N164">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N164" t="s">
+      <c r="O164" t="s">
         <v>32</v>
       </c>
-      <c r="O164">
+      <c r="P164">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q164" t="b">
@@ -11782,25 +11782,25 @@
       <c r="G165">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I165" t="s">
+      <c r="J165" t="s">
         <v>25</v>
       </c>
-      <c r="J165" t="s">
+      <c r="K165" t="s">
         <v>32</v>
       </c>
-      <c r="K165">
+      <c r="L165">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L165" t="s">
+      <c r="M165" t="s">
         <v>27</v>
       </c>
-      <c r="M165">
+      <c r="N165">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N165" t="s">
-        <v>33</v>
-      </c>
-      <c r="O165">
+      <c r="O165" t="s">
+        <v>33</v>
+      </c>
+      <c r="P165">
         <v>0</v>
       </c>
       <c r="Q165" t="b">
@@ -11847,25 +11847,25 @@
       <c r="G166">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I166" t="s">
+      <c r="J166" t="s">
         <v>25</v>
       </c>
-      <c r="J166" t="s">
-        <v>33</v>
-      </c>
-      <c r="K166">
-        <v>0</v>
-      </c>
-      <c r="L166" t="s">
+      <c r="K166" t="s">
+        <v>33</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166" t="s">
         <v>26</v>
       </c>
-      <c r="M166">
+      <c r="N166">
         <v>0.7142857142857143</v>
       </c>
-      <c r="N166" t="s">
-        <v>33</v>
-      </c>
-      <c r="O166">
+      <c r="O166" t="s">
+        <v>33</v>
+      </c>
+      <c r="P166">
         <v>0</v>
       </c>
       <c r="Q166" t="b">
@@ -11912,25 +11912,25 @@
       <c r="G167">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I167" t="s">
+      <c r="J167" t="s">
         <v>25</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>32</v>
       </c>
-      <c r="K167">
+      <c r="L167">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L167" t="s">
-        <v>28</v>
-      </c>
-      <c r="M167">
-        <v>1</v>
-      </c>
-      <c r="N167" t="s">
+      <c r="M167" t="s">
+        <v>28</v>
+      </c>
+      <c r="N167">
+        <v>1</v>
+      </c>
+      <c r="O167" t="s">
         <v>26</v>
       </c>
-      <c r="O167">
+      <c r="P167">
         <v>0.7142857142857143</v>
       </c>
       <c r="Q167" t="b">
@@ -11977,25 +11977,25 @@
       <c r="G168">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I168" t="s">
+      <c r="J168" t="s">
         <v>25</v>
       </c>
-      <c r="J168" t="s">
+      <c r="K168" t="s">
         <v>32</v>
       </c>
-      <c r="K168">
+      <c r="L168">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L168" t="s">
-        <v>28</v>
-      </c>
-      <c r="M168">
-        <v>1</v>
-      </c>
-      <c r="N168" t="s">
+      <c r="M168" t="s">
+        <v>28</v>
+      </c>
+      <c r="N168">
+        <v>1</v>
+      </c>
+      <c r="O168" t="s">
         <v>31</v>
       </c>
-      <c r="O168">
+      <c r="P168">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q168" t="b">
@@ -12042,25 +12042,25 @@
       <c r="G169">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I169" t="s">
+      <c r="J169" t="s">
         <v>25</v>
       </c>
-      <c r="J169" t="s">
+      <c r="K169" t="s">
         <v>31</v>
       </c>
-      <c r="K169">
+      <c r="L169">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L169" t="s">
-        <v>28</v>
-      </c>
-      <c r="M169">
-        <v>1</v>
-      </c>
-      <c r="N169" t="s">
+      <c r="M169" t="s">
+        <v>28</v>
+      </c>
+      <c r="N169">
+        <v>1</v>
+      </c>
+      <c r="O169" t="s">
         <v>27</v>
       </c>
-      <c r="O169">
+      <c r="P169">
         <v>0.8571428571428571</v>
       </c>
       <c r="Q169" t="b">
@@ -12107,25 +12107,25 @@
       <c r="G170">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I170" t="s">
+      <c r="J170" t="s">
         <v>25</v>
       </c>
-      <c r="J170" t="s">
-        <v>33</v>
-      </c>
-      <c r="K170">
-        <v>0</v>
-      </c>
-      <c r="L170" t="s">
-        <v>28</v>
-      </c>
-      <c r="M170">
-        <v>1</v>
-      </c>
-      <c r="N170" t="s">
-        <v>28</v>
-      </c>
-      <c r="O170">
+      <c r="K170" t="s">
+        <v>33</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170" t="s">
+        <v>28</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170" t="s">
+        <v>28</v>
+      </c>
+      <c r="P170">
         <v>1</v>
       </c>
       <c r="Q170" t="b">
@@ -12172,25 +12172,25 @@
       <c r="G171">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I171" t="s">
+      <c r="J171" t="s">
         <v>25</v>
       </c>
-      <c r="J171" t="s">
-        <v>33</v>
-      </c>
-      <c r="K171">
-        <v>0</v>
-      </c>
-      <c r="L171" t="s">
-        <v>28</v>
-      </c>
-      <c r="M171">
-        <v>1</v>
-      </c>
-      <c r="N171" t="s">
+      <c r="K171" t="s">
+        <v>33</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171" t="s">
+        <v>28</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171" t="s">
         <v>31</v>
       </c>
-      <c r="O171">
+      <c r="P171">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q171" t="b">
@@ -12237,25 +12237,25 @@
       <c r="G172">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I172" t="s">
+      <c r="J172" t="s">
         <v>25</v>
       </c>
-      <c r="J172" t="s">
+      <c r="K172" t="s">
         <v>31</v>
       </c>
-      <c r="K172">
+      <c r="L172">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L172" t="s">
-        <v>33</v>
-      </c>
-      <c r="M172">
-        <v>0</v>
-      </c>
-      <c r="N172" t="s">
-        <v>33</v>
-      </c>
-      <c r="O172">
+      <c r="M172" t="s">
+        <v>33</v>
+      </c>
+      <c r="N172">
+        <v>0</v>
+      </c>
+      <c r="O172" t="s">
+        <v>33</v>
+      </c>
+      <c r="P172">
         <v>0</v>
       </c>
       <c r="Q172" t="b">
@@ -12302,25 +12302,25 @@
       <c r="G173">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I173" t="s">
+      <c r="J173" t="s">
         <v>25</v>
       </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>31</v>
       </c>
-      <c r="K173">
+      <c r="L173">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L173" t="s">
-        <v>28</v>
-      </c>
-      <c r="M173">
-        <v>1</v>
-      </c>
-      <c r="N173" t="s">
+      <c r="M173" t="s">
+        <v>28</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173" t="s">
         <v>32</v>
       </c>
-      <c r="O173">
+      <c r="P173">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q173" t="b">
@@ -12367,25 +12367,25 @@
       <c r="G174">
         <v>0.8048962451751512</v>
       </c>
-      <c r="I174" t="s">
+      <c r="J174" t="s">
         <v>25</v>
       </c>
-      <c r="J174" t="s">
-        <v>33</v>
-      </c>
-      <c r="K174">
-        <v>0</v>
-      </c>
-      <c r="L174" t="s">
+      <c r="K174" t="s">
+        <v>33</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174" t="s">
         <v>27</v>
       </c>
-      <c r="M174">
+      <c r="N174">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N174" t="s">
-        <v>33</v>
-      </c>
-      <c r="O174">
+      <c r="O174" t="s">
+        <v>33</v>
+      </c>
+      <c r="P174">
         <v>0</v>
       </c>
       <c r="Q174" t="b">
@@ -12432,25 +12432,25 @@
       <c r="G175">
         <v>2.838098186555688</v>
       </c>
-      <c r="I175" t="s">
+      <c r="J175" t="s">
         <v>25</v>
       </c>
-      <c r="J175" t="s">
-        <v>33</v>
-      </c>
-      <c r="K175">
-        <v>0</v>
-      </c>
-      <c r="L175" t="s">
+      <c r="K175" t="s">
+        <v>33</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175" t="s">
         <v>31</v>
       </c>
-      <c r="M175">
+      <c r="N175">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N175" t="s">
-        <v>33</v>
-      </c>
-      <c r="O175">
+      <c r="O175" t="s">
+        <v>33</v>
+      </c>
+      <c r="P175">
         <v>0</v>
       </c>
       <c r="Q175" t="b">
@@ -12497,25 +12497,25 @@
       <c r="G176">
         <v>2.838098186555688</v>
       </c>
-      <c r="I176" t="s">
+      <c r="J176" t="s">
         <v>25</v>
       </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>26</v>
       </c>
-      <c r="K176">
+      <c r="L176">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L176" t="s">
-        <v>28</v>
-      </c>
-      <c r="M176">
-        <v>1</v>
-      </c>
-      <c r="N176" t="s">
+      <c r="M176" t="s">
+        <v>28</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
         <v>32</v>
       </c>
-      <c r="O176">
+      <c r="P176">
         <v>0.2857142857142857</v>
       </c>
       <c r="Q176" t="b">
@@ -12562,25 +12562,25 @@
       <c r="G177">
         <v>2.838098186555688</v>
       </c>
-      <c r="I177" t="s">
+      <c r="J177" t="s">
         <v>25</v>
       </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>30</v>
       </c>
-      <c r="K177">
+      <c r="L177">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L177" t="s">
-        <v>28</v>
-      </c>
-      <c r="M177">
-        <v>1</v>
-      </c>
-      <c r="N177" t="s">
+      <c r="M177" t="s">
+        <v>28</v>
+      </c>
+      <c r="N177">
+        <v>1</v>
+      </c>
+      <c r="O177" t="s">
         <v>30</v>
       </c>
-      <c r="O177">
+      <c r="P177">
         <v>0.4285714285714285</v>
       </c>
       <c r="Q177" t="b">
@@ -12627,25 +12627,25 @@
       <c r="G178">
         <v>2.838098186555688</v>
       </c>
-      <c r="I178" t="s">
+      <c r="J178" t="s">
         <v>25</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>26</v>
       </c>
-      <c r="K178">
+      <c r="L178">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L178" t="s">
-        <v>28</v>
-      </c>
-      <c r="M178">
-        <v>1</v>
-      </c>
-      <c r="N178" t="s">
+      <c r="M178" t="s">
+        <v>28</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
         <v>31</v>
       </c>
-      <c r="O178">
+      <c r="P178">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q178" t="b">
@@ -12692,25 +12692,25 @@
       <c r="G179">
         <v>2.838098186555688</v>
       </c>
-      <c r="I179" t="s">
+      <c r="J179" t="s">
         <v>25</v>
       </c>
-      <c r="J179" t="s">
-        <v>33</v>
-      </c>
-      <c r="K179">
-        <v>0</v>
-      </c>
-      <c r="L179" t="s">
-        <v>28</v>
-      </c>
-      <c r="M179">
-        <v>1</v>
-      </c>
-      <c r="N179" t="s">
-        <v>28</v>
-      </c>
-      <c r="O179">
+      <c r="K179" t="s">
+        <v>33</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179" t="s">
+        <v>28</v>
+      </c>
+      <c r="N179">
+        <v>1</v>
+      </c>
+      <c r="O179" t="s">
+        <v>28</v>
+      </c>
+      <c r="P179">
         <v>1</v>
       </c>
       <c r="Q179" t="b">
@@ -12757,25 +12757,25 @@
       <c r="G180">
         <v>2.838098186555688</v>
       </c>
-      <c r="I180" t="s">
+      <c r="J180" t="s">
         <v>25</v>
       </c>
-      <c r="J180" t="s">
+      <c r="K180" t="s">
         <v>32</v>
       </c>
-      <c r="K180">
+      <c r="L180">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L180" t="s">
-        <v>33</v>
-      </c>
-      <c r="M180">
-        <v>0</v>
-      </c>
-      <c r="N180" t="s">
-        <v>33</v>
-      </c>
-      <c r="O180">
+      <c r="M180" t="s">
+        <v>33</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180" t="s">
+        <v>33</v>
+      </c>
+      <c r="P180">
         <v>0</v>
       </c>
       <c r="Q180" t="b">
@@ -12822,25 +12822,25 @@
       <c r="G181">
         <v>2.838098186555688</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>25</v>
       </c>
-      <c r="J181" t="s">
+      <c r="K181" t="s">
         <v>26</v>
       </c>
-      <c r="K181">
+      <c r="L181">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L181" t="s">
-        <v>28</v>
-      </c>
-      <c r="M181">
-        <v>1</v>
-      </c>
-      <c r="N181" t="s">
-        <v>33</v>
-      </c>
-      <c r="O181">
+      <c r="M181" t="s">
+        <v>28</v>
+      </c>
+      <c r="N181">
+        <v>1</v>
+      </c>
+      <c r="O181" t="s">
+        <v>33</v>
+      </c>
+      <c r="P181">
         <v>0</v>
       </c>
       <c r="Q181" t="b">
@@ -12887,25 +12887,25 @@
       <c r="G182">
         <v>2.838098186555688</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>25</v>
       </c>
-      <c r="J182" t="s">
-        <v>33</v>
-      </c>
-      <c r="K182">
-        <v>0</v>
-      </c>
-      <c r="L182" t="s">
+      <c r="K182" t="s">
+        <v>33</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182" t="s">
         <v>27</v>
       </c>
-      <c r="M182">
+      <c r="N182">
         <v>0.8571428571428571</v>
       </c>
-      <c r="N182" t="s">
-        <v>33</v>
-      </c>
-      <c r="O182">
+      <c r="O182" t="s">
+        <v>33</v>
+      </c>
+      <c r="P182">
         <v>0</v>
       </c>
       <c r="Q182" t="b">
@@ -12952,25 +12952,25 @@
       <c r="G183">
         <v>2.838098186555688</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>25</v>
       </c>
-      <c r="J183" t="s">
+      <c r="K183" t="s">
         <v>30</v>
       </c>
-      <c r="K183">
+      <c r="L183">
         <v>0.4285714285714285</v>
       </c>
-      <c r="L183" t="s">
-        <v>28</v>
-      </c>
-      <c r="M183">
-        <v>1</v>
-      </c>
-      <c r="N183" t="s">
-        <v>33</v>
-      </c>
-      <c r="O183">
+      <c r="M183" t="s">
+        <v>28</v>
+      </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
+      <c r="O183" t="s">
+        <v>33</v>
+      </c>
+      <c r="P183">
         <v>0</v>
       </c>
       <c r="Q183" t="b">
@@ -13017,25 +13017,25 @@
       <c r="G184">
         <v>2.838098186555688</v>
       </c>
-      <c r="I184" t="s">
+      <c r="J184" t="s">
         <v>25</v>
       </c>
-      <c r="J184" t="s">
+      <c r="K184" t="s">
         <v>32</v>
       </c>
-      <c r="K184">
+      <c r="L184">
         <v>0.2857142857142857</v>
       </c>
-      <c r="L184" t="s">
-        <v>28</v>
-      </c>
-      <c r="M184">
-        <v>1</v>
-      </c>
-      <c r="N184" t="s">
+      <c r="M184" t="s">
+        <v>28</v>
+      </c>
+      <c r="N184">
+        <v>1</v>
+      </c>
+      <c r="O184" t="s">
         <v>31</v>
       </c>
-      <c r="O184">
+      <c r="P184">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q184" t="b">
@@ -13082,25 +13082,25 @@
       <c r="G185">
         <v>1.213154953565973</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>25</v>
       </c>
-      <c r="J185" t="s">
-        <v>33</v>
-      </c>
-      <c r="K185">
-        <v>0</v>
-      </c>
-      <c r="L185" t="s">
-        <v>33</v>
-      </c>
-      <c r="M185">
-        <v>0</v>
-      </c>
-      <c r="N185" t="s">
-        <v>33</v>
-      </c>
-      <c r="O185">
+      <c r="K185" t="s">
+        <v>33</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185" t="s">
+        <v>33</v>
+      </c>
+      <c r="N185">
+        <v>0</v>
+      </c>
+      <c r="O185" t="s">
+        <v>33</v>
+      </c>
+      <c r="P185">
         <v>0</v>
       </c>
       <c r="Q185" t="b">
@@ -13147,25 +13147,25 @@
       <c r="G186">
         <v>1.213154953565973</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>25</v>
       </c>
-      <c r="J186" t="s">
-        <v>33</v>
-      </c>
-      <c r="K186">
-        <v>0</v>
-      </c>
-      <c r="L186" t="s">
-        <v>28</v>
-      </c>
-      <c r="M186">
-        <v>1</v>
-      </c>
-      <c r="N186" t="s">
+      <c r="K186" t="s">
+        <v>33</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186" t="s">
+        <v>28</v>
+      </c>
+      <c r="N186">
+        <v>1</v>
+      </c>
+      <c r="O186" t="s">
         <v>31</v>
       </c>
-      <c r="O186">
+      <c r="P186">
         <v>0.1428571428571428</v>
       </c>
       <c r="Q186" t="b">
@@ -13212,25 +13212,25 @@
       <c r="G187">
         <v>1.213154953565973</v>
       </c>
-      <c r="I187" t="s">
+      <c r="J187" t="s">
         <v>25</v>
       </c>
-      <c r="J187" t="s">
-        <v>28</v>
-      </c>
-      <c r="K187">
-        <v>1</v>
-      </c>
-      <c r="L187" t="s">
-        <v>28</v>
-      </c>
-      <c r="M187">
-        <v>1</v>
-      </c>
-      <c r="N187" t="s">
-        <v>33</v>
-      </c>
-      <c r="O187">
+      <c r="K187" t="s">
+        <v>28</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="M187" t="s">
+        <v>28</v>
+      </c>
+      <c r="N187">
+        <v>1</v>
+      </c>
+      <c r="O187" t="s">
+        <v>33</v>
+      </c>
+      <c r="P187">
         <v>0</v>
       </c>
       <c r="Q187" t="b">
@@ -13277,25 +13277,25 @@
       <c r="G188">
         <v>1.213154953565973</v>
       </c>
-      <c r="I188" t="s">
+      <c r="J188" t="s">
         <v>25</v>
       </c>
-      <c r="J188" t="s">
-        <v>28</v>
-      </c>
-      <c r="K188">
-        <v>1</v>
-      </c>
-      <c r="L188" t="s">
-        <v>28</v>
-      </c>
-      <c r="M188">
-        <v>1</v>
-      </c>
-      <c r="N188" t="s">
-        <v>33</v>
-      </c>
-      <c r="O188">
+      <c r="K188" t="s">
+        <v>28</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188" t="s">
+        <v>28</v>
+      </c>
+      <c r="N188">
+        <v>1</v>
+      </c>
+      <c r="O188" t="s">
+        <v>33</v>
+      </c>
+      <c r="P188">
         <v>0</v>
       </c>
       <c r="Q188" t="b">
@@ -13342,25 +13342,25 @@
       <c r="G189">
         <v>1.213154953565973</v>
       </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>25</v>
       </c>
-      <c r="J189" t="s">
-        <v>28</v>
-      </c>
-      <c r="K189">
-        <v>1</v>
-      </c>
-      <c r="L189" t="s">
-        <v>28</v>
-      </c>
-      <c r="M189">
-        <v>1</v>
-      </c>
-      <c r="N189" t="s">
-        <v>33</v>
-      </c>
-      <c r="O189">
+      <c r="K189" t="s">
+        <v>28</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189" t="s">
+        <v>28</v>
+      </c>
+      <c r="N189">
+        <v>1</v>
+      </c>
+      <c r="O189" t="s">
+        <v>33</v>
+      </c>
+      <c r="P189">
         <v>0</v>
       </c>
       <c r="Q189" t="b">
@@ -13407,25 +13407,25 @@
       <c r="G190">
         <v>1.213154953565973</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>25</v>
       </c>
-      <c r="J190" t="s">
-        <v>28</v>
-      </c>
-      <c r="K190">
-        <v>1</v>
-      </c>
-      <c r="L190" t="s">
-        <v>28</v>
-      </c>
-      <c r="M190">
-        <v>1</v>
-      </c>
-      <c r="N190" t="s">
-        <v>33</v>
-      </c>
-      <c r="O190">
+      <c r="K190" t="s">
+        <v>28</v>
+      </c>
+      <c r="L190">
+        <v>1</v>
+      </c>
+      <c r="M190" t="s">
+        <v>28</v>
+      </c>
+      <c r="N190">
+        <v>1</v>
+      </c>
+      <c r="O190" t="s">
+        <v>33</v>
+      </c>
+      <c r="P190">
         <v>0</v>
       </c>
       <c r="Q190" t="b">
@@ -13472,25 +13472,25 @@
       <c r="G191">
         <v>1.213154953565973</v>
       </c>
-      <c r="I191" t="s">
+      <c r="J191" t="s">
         <v>25</v>
       </c>
-      <c r="J191" t="s">
+      <c r="K191" t="s">
         <v>31</v>
       </c>
-      <c r="K191">
+      <c r="L191">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L191" t="s">
+      <c r="M191" t="s">
         <v>32</v>
       </c>
-      <c r="M191">
+      <c r="N191">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N191" t="s">
-        <v>33</v>
-      </c>
-      <c r="O191">
+      <c r="O191" t="s">
+        <v>33</v>
+      </c>
+      <c r="P191">
         <v>0</v>
       </c>
       <c r="Q191" t="b">
@@ -13537,25 +13537,25 @@
       <c r="G192">
         <v>1.213154953565973</v>
       </c>
-      <c r="I192" t="s">
+      <c r="J192" t="s">
         <v>25</v>
       </c>
-      <c r="J192" t="s">
-        <v>28</v>
-      </c>
-      <c r="K192">
-        <v>1</v>
-      </c>
-      <c r="L192" t="s">
-        <v>28</v>
-      </c>
-      <c r="M192">
-        <v>1</v>
-      </c>
-      <c r="N192" t="s">
-        <v>33</v>
-      </c>
-      <c r="O192">
+      <c r="K192" t="s">
+        <v>28</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192" t="s">
+        <v>28</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>33</v>
+      </c>
+      <c r="P192">
         <v>0</v>
       </c>
       <c r="Q192" t="b">
@@ -13602,25 +13602,25 @@
       <c r="G193">
         <v>1.213154953565973</v>
       </c>
-      <c r="I193" t="s">
+      <c r="J193" t="s">
         <v>25</v>
       </c>
-      <c r="J193" t="s">
-        <v>28</v>
-      </c>
-      <c r="K193">
-        <v>1</v>
-      </c>
-      <c r="L193" t="s">
-        <v>28</v>
-      </c>
-      <c r="M193">
-        <v>1</v>
-      </c>
-      <c r="N193" t="s">
-        <v>33</v>
-      </c>
-      <c r="O193">
+      <c r="K193" t="s">
+        <v>28</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="M193" t="s">
+        <v>28</v>
+      </c>
+      <c r="N193">
+        <v>1</v>
+      </c>
+      <c r="O193" t="s">
+        <v>33</v>
+      </c>
+      <c r="P193">
         <v>0</v>
       </c>
       <c r="Q193" t="b">
@@ -13667,25 +13667,25 @@
       <c r="G194">
         <v>1.213154953565973</v>
       </c>
-      <c r="I194" t="s">
+      <c r="J194" t="s">
         <v>25</v>
       </c>
-      <c r="J194" t="s">
-        <v>28</v>
-      </c>
-      <c r="K194">
-        <v>1</v>
-      </c>
-      <c r="L194" t="s">
-        <v>28</v>
-      </c>
-      <c r="M194">
-        <v>1</v>
-      </c>
-      <c r="N194" t="s">
-        <v>33</v>
-      </c>
-      <c r="O194">
+      <c r="K194" t="s">
+        <v>28</v>
+      </c>
+      <c r="L194">
+        <v>1</v>
+      </c>
+      <c r="M194" t="s">
+        <v>28</v>
+      </c>
+      <c r="N194">
+        <v>1</v>
+      </c>
+      <c r="O194" t="s">
+        <v>33</v>
+      </c>
+      <c r="P194">
         <v>0</v>
       </c>
       <c r="Q194" t="b">
@@ -13732,25 +13732,25 @@
       <c r="G195">
         <v>1.213154953565973</v>
       </c>
-      <c r="I195" t="s">
+      <c r="J195" t="s">
         <v>25</v>
       </c>
-      <c r="J195" t="s">
+      <c r="K195" t="s">
         <v>26</v>
       </c>
-      <c r="K195">
+      <c r="L195">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L195" t="s">
-        <v>28</v>
-      </c>
-      <c r="M195">
-        <v>1</v>
-      </c>
-      <c r="N195" t="s">
-        <v>33</v>
-      </c>
-      <c r="O195">
+      <c r="M195" t="s">
+        <v>28</v>
+      </c>
+      <c r="N195">
+        <v>1</v>
+      </c>
+      <c r="O195" t="s">
+        <v>33</v>
+      </c>
+      <c r="P195">
         <v>0</v>
       </c>
       <c r="Q195" t="b">
@@ -13797,25 +13797,25 @@
       <c r="G196">
         <v>1.213154953565973</v>
       </c>
-      <c r="I196" t="s">
+      <c r="J196" t="s">
         <v>25</v>
       </c>
-      <c r="J196" t="s">
-        <v>28</v>
-      </c>
-      <c r="K196">
-        <v>1</v>
-      </c>
-      <c r="L196" t="s">
-        <v>28</v>
-      </c>
-      <c r="M196">
-        <v>1</v>
-      </c>
-      <c r="N196" t="s">
-        <v>33</v>
-      </c>
-      <c r="O196">
+      <c r="K196" t="s">
+        <v>28</v>
+      </c>
+      <c r="L196">
+        <v>1</v>
+      </c>
+      <c r="M196" t="s">
+        <v>28</v>
+      </c>
+      <c r="N196">
+        <v>1</v>
+      </c>
+      <c r="O196" t="s">
+        <v>33</v>
+      </c>
+      <c r="P196">
         <v>0</v>
       </c>
       <c r="Q196" t="b">
@@ -13862,25 +13862,25 @@
       <c r="G197">
         <v>1.213154953565973</v>
       </c>
-      <c r="I197" t="s">
+      <c r="J197" t="s">
         <v>25</v>
       </c>
-      <c r="J197" t="s">
+      <c r="K197" t="s">
         <v>31</v>
       </c>
-      <c r="K197">
+      <c r="L197">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L197" t="s">
+      <c r="M197" t="s">
         <v>31</v>
       </c>
-      <c r="M197">
+      <c r="N197">
         <v>0.1428571428571428</v>
       </c>
-      <c r="N197" t="s">
-        <v>33</v>
-      </c>
-      <c r="O197">
+      <c r="O197" t="s">
+        <v>33</v>
+      </c>
+      <c r="P197">
         <v>0</v>
       </c>
       <c r="Q197" t="b">
@@ -13927,25 +13927,25 @@
       <c r="G198">
         <v>1.213154953565973</v>
       </c>
-      <c r="I198" t="s">
+      <c r="J198" t="s">
         <v>25</v>
       </c>
-      <c r="J198" t="s">
-        <v>28</v>
-      </c>
-      <c r="K198">
-        <v>1</v>
-      </c>
-      <c r="L198" t="s">
-        <v>33</v>
-      </c>
-      <c r="M198">
-        <v>0</v>
-      </c>
-      <c r="N198" t="s">
-        <v>33</v>
-      </c>
-      <c r="O198">
+      <c r="K198" t="s">
+        <v>28</v>
+      </c>
+      <c r="L198">
+        <v>1</v>
+      </c>
+      <c r="M198" t="s">
+        <v>33</v>
+      </c>
+      <c r="N198">
+        <v>0</v>
+      </c>
+      <c r="O198" t="s">
+        <v>33</v>
+      </c>
+      <c r="P198">
         <v>0</v>
       </c>
       <c r="Q198" t="b">
@@ -13992,25 +13992,25 @@
       <c r="G199">
         <v>1.213154953565973</v>
       </c>
-      <c r="I199" t="s">
+      <c r="J199" t="s">
         <v>25</v>
       </c>
-      <c r="J199" t="s">
-        <v>28</v>
-      </c>
-      <c r="K199">
-        <v>1</v>
-      </c>
-      <c r="L199" t="s">
-        <v>28</v>
-      </c>
-      <c r="M199">
-        <v>1</v>
-      </c>
-      <c r="N199" t="s">
-        <v>33</v>
-      </c>
-      <c r="O199">
+      <c r="K199" t="s">
+        <v>28</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="M199" t="s">
+        <v>28</v>
+      </c>
+      <c r="N199">
+        <v>1</v>
+      </c>
+      <c r="O199" t="s">
+        <v>33</v>
+      </c>
+      <c r="P199">
         <v>0</v>
       </c>
       <c r="Q199" t="b">
@@ -14057,25 +14057,25 @@
       <c r="G200">
         <v>1.213154953565973</v>
       </c>
-      <c r="I200" t="s">
+      <c r="J200" t="s">
         <v>25</v>
       </c>
-      <c r="J200" t="s">
+      <c r="K200" t="s">
         <v>31</v>
       </c>
-      <c r="K200">
+      <c r="L200">
         <v>0.1428571428571428</v>
       </c>
-      <c r="L200" t="s">
-        <v>33</v>
-      </c>
-      <c r="M200">
-        <v>0</v>
-      </c>
-      <c r="N200" t="s">
-        <v>33</v>
-      </c>
-      <c r="O200">
+      <c r="M200" t="s">
+        <v>33</v>
+      </c>
+      <c r="N200">
+        <v>0</v>
+      </c>
+      <c r="O200" t="s">
+        <v>33</v>
+      </c>
+      <c r="P200">
         <v>0</v>
       </c>
       <c r="Q200" t="b">
@@ -14122,25 +14122,25 @@
       <c r="G201">
         <v>1.213154953565973</v>
       </c>
-      <c r="I201" t="s">
+      <c r="J201" t="s">
         <v>25</v>
       </c>
-      <c r="J201" t="s">
-        <v>28</v>
-      </c>
-      <c r="K201">
-        <v>1</v>
-      </c>
-      <c r="L201" t="s">
-        <v>28</v>
-      </c>
-      <c r="M201">
-        <v>1</v>
-      </c>
-      <c r="N201" t="s">
-        <v>33</v>
-      </c>
-      <c r="O201">
+      <c r="K201" t="s">
+        <v>28</v>
+      </c>
+      <c r="L201">
+        <v>1</v>
+      </c>
+      <c r="M201" t="s">
+        <v>28</v>
+      </c>
+      <c r="N201">
+        <v>1</v>
+      </c>
+      <c r="O201" t="s">
+        <v>33</v>
+      </c>
+      <c r="P201">
         <v>0</v>
       </c>
       <c r="Q201" t="b">
@@ -14187,25 +14187,25 @@
       <c r="G202">
         <v>1.213154953565973</v>
       </c>
-      <c r="I202" t="s">
+      <c r="J202" t="s">
         <v>25</v>
       </c>
-      <c r="J202" t="s">
-        <v>28</v>
-      </c>
-      <c r="K202">
-        <v>1</v>
-      </c>
-      <c r="L202" t="s">
-        <v>28</v>
-      </c>
-      <c r="M202">
-        <v>1</v>
-      </c>
-      <c r="N202" t="s">
-        <v>33</v>
-      </c>
-      <c r="O202">
+      <c r="K202" t="s">
+        <v>28</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202" t="s">
+        <v>28</v>
+      </c>
+      <c r="N202">
+        <v>1</v>
+      </c>
+      <c r="O202" t="s">
+        <v>33</v>
+      </c>
+      <c r="P202">
         <v>0</v>
       </c>
       <c r="Q202" t="b">
@@ -14252,25 +14252,25 @@
       <c r="G203">
         <v>1.213154953565973</v>
       </c>
-      <c r="I203" t="s">
+      <c r="J203" t="s">
         <v>25</v>
       </c>
-      <c r="J203" t="s">
-        <v>28</v>
-      </c>
-      <c r="K203">
-        <v>1</v>
-      </c>
-      <c r="L203" t="s">
-        <v>28</v>
-      </c>
-      <c r="M203">
-        <v>1</v>
-      </c>
-      <c r="N203" t="s">
-        <v>33</v>
-      </c>
-      <c r="O203">
+      <c r="K203" t="s">
+        <v>28</v>
+      </c>
+      <c r="L203">
+        <v>1</v>
+      </c>
+      <c r="M203" t="s">
+        <v>28</v>
+      </c>
+      <c r="N203">
+        <v>1</v>
+      </c>
+      <c r="O203" t="s">
+        <v>33</v>
+      </c>
+      <c r="P203">
         <v>0</v>
       </c>
       <c r="Q203" t="b">
@@ -14317,25 +14317,25 @@
       <c r="G204">
         <v>1.213154953565973</v>
       </c>
-      <c r="I204" t="s">
+      <c r="J204" t="s">
         <v>25</v>
       </c>
-      <c r="J204" t="s">
-        <v>28</v>
-      </c>
-      <c r="K204">
-        <v>1</v>
-      </c>
-      <c r="L204" t="s">
-        <v>28</v>
-      </c>
-      <c r="M204">
-        <v>1</v>
-      </c>
-      <c r="N204" t="s">
-        <v>33</v>
-      </c>
-      <c r="O204">
+      <c r="K204" t="s">
+        <v>28</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="M204" t="s">
+        <v>28</v>
+      </c>
+      <c r="N204">
+        <v>1</v>
+      </c>
+      <c r="O204" t="s">
+        <v>33</v>
+      </c>
+      <c r="P204">
         <v>0</v>
       </c>
       <c r="Q204" t="b">
@@ -14382,25 +14382,25 @@
       <c r="G205">
         <v>1.213154953565973</v>
       </c>
-      <c r="I205" t="s">
+      <c r="J205" t="s">
         <v>25</v>
       </c>
-      <c r="J205" t="s">
-        <v>28</v>
-      </c>
-      <c r="K205">
-        <v>1</v>
-      </c>
-      <c r="L205" t="s">
-        <v>28</v>
-      </c>
-      <c r="M205">
-        <v>1</v>
-      </c>
-      <c r="N205" t="s">
-        <v>33</v>
-      </c>
-      <c r="O205">
+      <c r="K205" t="s">
+        <v>28</v>
+      </c>
+      <c r="L205">
+        <v>1</v>
+      </c>
+      <c r="M205" t="s">
+        <v>28</v>
+      </c>
+      <c r="N205">
+        <v>1</v>
+      </c>
+      <c r="O205" t="s">
+        <v>33</v>
+      </c>
+      <c r="P205">
         <v>0</v>
       </c>
       <c r="Q205" t="b">
@@ -14447,25 +14447,25 @@
       <c r="G206">
         <v>1.213154953565973</v>
       </c>
-      <c r="I206" t="s">
+      <c r="J206" t="s">
         <v>25</v>
       </c>
-      <c r="J206" t="s">
-        <v>28</v>
-      </c>
-      <c r="K206">
-        <v>1</v>
-      </c>
-      <c r="L206" t="s">
-        <v>28</v>
-      </c>
-      <c r="M206">
-        <v>1</v>
-      </c>
-      <c r="N206" t="s">
-        <v>33</v>
-      </c>
-      <c r="O206">
+      <c r="K206" t="s">
+        <v>28</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="M206" t="s">
+        <v>28</v>
+      </c>
+      <c r="N206">
+        <v>1</v>
+      </c>
+      <c r="O206" t="s">
+        <v>33</v>
+      </c>
+      <c r="P206">
         <v>0</v>
       </c>
       <c r="Q206" t="b">
@@ -14512,25 +14512,25 @@
       <c r="G207">
         <v>1.213154953565973</v>
       </c>
-      <c r="I207" t="s">
+      <c r="J207" t="s">
         <v>25</v>
       </c>
-      <c r="J207" t="s">
-        <v>28</v>
-      </c>
-      <c r="K207">
-        <v>1</v>
-      </c>
-      <c r="L207" t="s">
-        <v>28</v>
-      </c>
-      <c r="M207">
-        <v>1</v>
-      </c>
-      <c r="N207" t="s">
-        <v>33</v>
-      </c>
-      <c r="O207">
+      <c r="K207" t="s">
+        <v>28</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="M207" t="s">
+        <v>28</v>
+      </c>
+      <c r="N207">
+        <v>1</v>
+      </c>
+      <c r="O207" t="s">
+        <v>33</v>
+      </c>
+      <c r="P207">
         <v>0</v>
       </c>
       <c r="Q207" t="b">

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_glass.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_glass.xlsx
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -671,7 +671,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="b">
         <v>1</v>
@@ -1026,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="b">
         <v>1</v>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="b">
         <v>1</v>
@@ -1339,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -1381,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="b">
         <v>1</v>
@@ -1390,7 +1390,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1410,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>7</v>
@@ -1452,7 +1452,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="b">
         <v>1</v>
@@ -1481,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1523,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="b">
         <v>1</v>
@@ -1532,7 +1532,7 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1694,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -1736,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="b">
         <v>1</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="b">
         <v>1</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="b">
         <v>1</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="b">
         <v>1</v>
@@ -2049,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>7</v>
@@ -2091,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="b">
         <v>1</v>
@@ -2120,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2162,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="b">
         <v>1</v>
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -2262,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2304,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="b">
         <v>1</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="b">
         <v>1</v>
@@ -2404,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -2443,10 +2443,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="b">
         <v>1</v>
@@ -2475,7 +2475,7 @@
         <v>1</v>
       </c>
       <c r="D29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>7</v>
@@ -2517,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="b">
         <v>1</v>
@@ -2588,10 +2588,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -2617,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="D31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -2659,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="b">
         <v>1</v>
@@ -2668,7 +2668,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -2730,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="b">
         <v>1</v>
@@ -2804,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33">
         <v>5</v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="b">
         <v>1</v>
@@ -2943,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="b">
         <v>1</v>
@@ -3011,13 +3011,13 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36">
         <v>7</v>
@@ -3043,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="D37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>7</v>
@@ -3085,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="b">
         <v>1</v>
@@ -3185,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -3227,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="R39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="b">
         <v>1</v>
@@ -3256,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>7</v>
@@ -3298,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="R40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="b">
         <v>1</v>
@@ -3398,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>7</v>
@@ -3440,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="b">
         <v>1</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="b">
         <v>1</v>
@@ -3653,10 +3653,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45">
         <v>7</v>
@@ -3724,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="b">
         <v>1</v>
@@ -3753,7 +3753,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>7</v>
@@ -3795,7 +3795,7 @@
         <v>1</v>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="b">
         <v>1</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="b">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="D51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>7</v>
@@ -4079,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="b">
         <v>1</v>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="b">
         <v>1</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="R53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="b">
         <v>1</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" t="b">
         <v>1</v>
@@ -4321,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="D55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>7</v>
@@ -4363,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="R55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="b">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         <v>7</v>
       </c>
       <c r="U55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V55">
         <v>7</v>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="R58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="b">
         <v>1</v>
@@ -4644,10 +4644,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" t="b">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
       </c>
       <c r="S61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61">
         <v>5</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="R62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="b">
         <v>1</v>
@@ -5002,10 +5002,10 @@
         <v>0</v>
       </c>
       <c r="R64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64">
         <v>7</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="R65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="b">
         <v>1</v>
@@ -5141,10 +5141,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" t="b">
         <v>0</v>
@@ -5215,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="R67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" t="b">
         <v>0</v>
@@ -5286,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="R68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="b">
         <v>1</v>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="Q69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
@@ -5425,13 +5425,13 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="Q70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="b">
         <v>1</v>
@@ -5641,10 +5641,10 @@
         <v>1</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73">
         <v>7</v>
@@ -5712,10 +5712,10 @@
         <v>0</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74">
         <v>7</v>
@@ -5741,7 +5741,7 @@
         <v>5</v>
       </c>
       <c r="D75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>7</v>
@@ -5783,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="b">
         <v>1</v>
@@ -5792,7 +5792,7 @@
         <v>7</v>
       </c>
       <c r="U75">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V75">
         <v>7</v>
@@ -5854,10 +5854,10 @@
         <v>0</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76">
         <v>7</v>
@@ -5922,7 +5922,7 @@
         <v>0</v>
       </c>
       <c r="Q77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="b">
         <v>0</v>
@@ -5954,7 +5954,7 @@
         <v>5</v>
       </c>
       <c r="D78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>7</v>
@@ -5996,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="b">
         <v>1</v>
@@ -6005,7 +6005,7 @@
         <v>7</v>
       </c>
       <c r="U78">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V78">
         <v>7</v>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="R79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79" t="b">
         <v>1</v>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80" t="b">
         <v>1</v>
@@ -6167,7 +6167,7 @@
         <v>5</v>
       </c>
       <c r="D81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81">
         <v>7</v>
@@ -6206,10 +6206,10 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S81" t="b">
         <v>1</v>
@@ -6218,7 +6218,7 @@
         <v>7</v>
       </c>
       <c r="U81">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V81">
         <v>7</v>
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="R83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S83" t="b">
         <v>1</v>
@@ -6380,7 +6380,7 @@
         <v>7</v>
       </c>
       <c r="D84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84">
         <v>7</v>
@@ -6422,7 +6422,7 @@
         <v>1</v>
       </c>
       <c r="R84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="b">
         <v>1</v>
@@ -6431,7 +6431,7 @@
         <v>7</v>
       </c>
       <c r="U84">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V84">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>7</v>
       </c>
       <c r="D85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85">
         <v>7</v>
@@ -6493,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="R85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S85" t="b">
         <v>1</v>
@@ -6502,7 +6502,7 @@
         <v>7</v>
       </c>
       <c r="U85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85">
         <v>7</v>
@@ -6522,7 +6522,7 @@
         <v>7</v>
       </c>
       <c r="D86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>7</v>
@@ -6564,7 +6564,7 @@
         <v>1</v>
       </c>
       <c r="R86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" t="b">
         <v>1</v>
@@ -6573,7 +6573,7 @@
         <v>7</v>
       </c>
       <c r="U86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V86">
         <v>7</v>
@@ -6593,7 +6593,7 @@
         <v>7</v>
       </c>
       <c r="D87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>7</v>
@@ -6635,7 +6635,7 @@
         <v>1</v>
       </c>
       <c r="R87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87" t="b">
         <v>1</v>
@@ -6644,7 +6644,7 @@
         <v>7</v>
       </c>
       <c r="U87">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V87">
         <v>7</v>
@@ -6735,7 +6735,7 @@
         <v>7</v>
       </c>
       <c r="D89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>7</v>
@@ -6777,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="R89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S89" t="b">
         <v>1</v>
@@ -6786,7 +6786,7 @@
         <v>7</v>
       </c>
       <c r="U89">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V89">
         <v>7</v>
@@ -6806,7 +6806,7 @@
         <v>7</v>
       </c>
       <c r="D90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>7</v>
@@ -6848,7 +6848,7 @@
         <v>1</v>
       </c>
       <c r="R90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="b">
         <v>1</v>
@@ -6857,7 +6857,7 @@
         <v>7</v>
       </c>
       <c r="U90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V90">
         <v>7</v>
@@ -6877,7 +6877,7 @@
         <v>7</v>
       </c>
       <c r="D91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>7</v>
@@ -6919,7 +6919,7 @@
         <v>1</v>
       </c>
       <c r="R91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="b">
         <v>1</v>
@@ -6928,7 +6928,7 @@
         <v>7</v>
       </c>
       <c r="U91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V91">
         <v>7</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="R92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S92" t="b">
         <v>1</v>
@@ -7019,7 +7019,7 @@
         <v>7</v>
       </c>
       <c r="D93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>7</v>
@@ -7061,7 +7061,7 @@
         <v>1</v>
       </c>
       <c r="R93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" t="b">
         <v>1</v>
@@ -7070,7 +7070,7 @@
         <v>7</v>
       </c>
       <c r="U93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V93">
         <v>7</v>
@@ -7232,7 +7232,7 @@
         <v>7</v>
       </c>
       <c r="D96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>7</v>
@@ -7274,7 +7274,7 @@
         <v>1</v>
       </c>
       <c r="R96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S96" t="b">
         <v>1</v>
@@ -7283,7 +7283,7 @@
         <v>7</v>
       </c>
       <c r="U96">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V96">
         <v>7</v>
@@ -7374,7 +7374,7 @@
         <v>7</v>
       </c>
       <c r="D98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>7</v>
@@ -7416,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="R98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="b">
         <v>1</v>
@@ -7425,7 +7425,7 @@
         <v>7</v>
       </c>
       <c r="U98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V98">
         <v>7</v>
@@ -7445,7 +7445,7 @@
         <v>7</v>
       </c>
       <c r="D99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>7</v>
@@ -7487,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="R99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="b">
         <v>1</v>
@@ -7496,7 +7496,7 @@
         <v>7</v>
       </c>
       <c r="U99">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V99">
         <v>7</v>
@@ -7516,7 +7516,7 @@
         <v>7</v>
       </c>
       <c r="D100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>7</v>
@@ -7558,7 +7558,7 @@
         <v>1</v>
       </c>
       <c r="R100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S100" t="b">
         <v>1</v>
@@ -7567,7 +7567,7 @@
         <v>7</v>
       </c>
       <c r="U100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V100">
         <v>7</v>
@@ -7587,7 +7587,7 @@
         <v>7</v>
       </c>
       <c r="D101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>7</v>
@@ -7629,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="R101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S101" t="b">
         <v>1</v>
@@ -7658,7 +7658,7 @@
         <v>7</v>
       </c>
       <c r="D102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>7</v>
@@ -7700,7 +7700,7 @@
         <v>1</v>
       </c>
       <c r="R102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S102" t="b">
         <v>1</v>
@@ -7709,7 +7709,7 @@
         <v>7</v>
       </c>
       <c r="U102">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V102">
         <v>7</v>
@@ -7729,7 +7729,7 @@
         <v>7</v>
       </c>
       <c r="D103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>7</v>
@@ -7771,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="R103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S103" t="b">
         <v>1</v>
@@ -7780,7 +7780,7 @@
         <v>7</v>
       </c>
       <c r="U103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V103">
         <v>7</v>
@@ -7800,7 +7800,7 @@
         <v>7</v>
       </c>
       <c r="D104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -7842,7 +7842,7 @@
         <v>1</v>
       </c>
       <c r="R104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S104" t="b">
         <v>1</v>
@@ -7851,7 +7851,7 @@
         <v>7</v>
       </c>
       <c r="U104">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V104">
         <v>7</v>
@@ -7936,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="D106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>7</v>
@@ -7972,7 +7972,7 @@
         <v>1</v>
       </c>
       <c r="R106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S106" t="b">
         <v>1</v>
@@ -8297,10 +8297,10 @@
         <v>1</v>
       </c>
       <c r="R111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111">
         <v>7</v>
@@ -8362,7 +8362,7 @@
         <v>0</v>
       </c>
       <c r="R112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S112" t="b">
         <v>1</v>
@@ -8427,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="R113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S113" t="b">
         <v>1</v>
@@ -8586,7 +8586,7 @@
         <v>1</v>
       </c>
       <c r="D116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>7</v>
@@ -8622,7 +8622,7 @@
         <v>1</v>
       </c>
       <c r="R116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S116" t="b">
         <v>1</v>
@@ -8651,7 +8651,7 @@
         <v>1</v>
       </c>
       <c r="D117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>7</v>
@@ -8687,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="R117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S117" t="b">
         <v>1</v>
@@ -8696,7 +8696,7 @@
         <v>6</v>
       </c>
       <c r="U117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V117">
         <v>6</v>
@@ -8716,7 +8716,7 @@
         <v>1</v>
       </c>
       <c r="D118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>7</v>
@@ -8752,7 +8752,7 @@
         <v>1</v>
       </c>
       <c r="R118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S118" t="b">
         <v>1</v>
@@ -8911,7 +8911,7 @@
         <v>1</v>
       </c>
       <c r="D121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>7</v>
@@ -8947,7 +8947,7 @@
         <v>1</v>
       </c>
       <c r="R121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="b">
         <v>1</v>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="R122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="b">
         <v>1</v>
@@ -9142,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="R124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S124" t="b">
         <v>1</v>
@@ -9171,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="D125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>7</v>
@@ -9207,7 +9207,7 @@
         <v>1</v>
       </c>
       <c r="R125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S125" t="b">
         <v>1</v>
@@ -9236,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="D126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>7</v>
@@ -9272,7 +9272,7 @@
         <v>1</v>
       </c>
       <c r="R126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S126" t="b">
         <v>1</v>
@@ -9281,7 +9281,7 @@
         <v>7</v>
       </c>
       <c r="U126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V126">
         <v>7</v>
@@ -9301,7 +9301,7 @@
         <v>1</v>
       </c>
       <c r="D127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>7</v>
@@ -9337,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="R127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S127" t="b">
         <v>1</v>
@@ -9431,7 +9431,7 @@
         <v>1</v>
       </c>
       <c r="D129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>7</v>
@@ -9467,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="R129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S129" t="b">
         <v>1</v>
@@ -9496,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="D130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>7</v>
@@ -9532,7 +9532,7 @@
         <v>1</v>
       </c>
       <c r="R130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S130" t="b">
         <v>1</v>
@@ -9597,7 +9597,7 @@
         <v>0</v>
       </c>
       <c r="R131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S131" t="b">
         <v>1</v>
@@ -9626,7 +9626,7 @@
         <v>1</v>
       </c>
       <c r="D132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>7</v>
@@ -9662,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="R132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S132" t="b">
         <v>1</v>
@@ -9671,7 +9671,7 @@
         <v>7</v>
       </c>
       <c r="U132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V132">
         <v>7</v>
@@ -9727,10 +9727,10 @@
         <v>1</v>
       </c>
       <c r="R133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133">
         <v>7</v>
@@ -9756,7 +9756,7 @@
         <v>1</v>
       </c>
       <c r="D134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>7</v>
@@ -9792,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="R134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S134" t="b">
         <v>1</v>
@@ -9821,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="D135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>7</v>
@@ -9857,7 +9857,7 @@
         <v>1</v>
       </c>
       <c r="R135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S135" t="b">
         <v>1</v>
@@ -9925,7 +9925,7 @@
         <v>0</v>
       </c>
       <c r="S136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136">
         <v>5</v>
@@ -9951,7 +9951,7 @@
         <v>1</v>
       </c>
       <c r="D137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>1</v>
       </c>
       <c r="R137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S137" t="b">
         <v>1</v>
@@ -10052,7 +10052,7 @@
         <v>0</v>
       </c>
       <c r="R138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S138" t="b">
         <v>1</v>
@@ -10117,10 +10117,10 @@
         <v>0</v>
       </c>
       <c r="R139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139">
         <v>7</v>
@@ -10146,7 +10146,7 @@
         <v>1</v>
       </c>
       <c r="D140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140">
         <v>7</v>
@@ -10182,7 +10182,7 @@
         <v>1</v>
       </c>
       <c r="R140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S140" t="b">
         <v>1</v>
@@ -10276,7 +10276,7 @@
         <v>1</v>
       </c>
       <c r="D142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>7</v>
@@ -10312,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="R142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S142" t="b">
         <v>1</v>
@@ -10341,7 +10341,7 @@
         <v>1</v>
       </c>
       <c r="D143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143">
         <v>7</v>
@@ -10377,7 +10377,7 @@
         <v>1</v>
       </c>
       <c r="R143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S143" t="b">
         <v>1</v>
@@ -10471,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="D145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145">
         <v>7</v>
@@ -10507,7 +10507,7 @@
         <v>1</v>
       </c>
       <c r="R145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S145" t="b">
         <v>1</v>
@@ -10572,7 +10572,7 @@
         <v>0</v>
       </c>
       <c r="R146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S146" t="b">
         <v>1</v>
@@ -10702,10 +10702,10 @@
         <v>0</v>
       </c>
       <c r="R148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T148">
         <v>7</v>
@@ -10731,7 +10731,7 @@
         <v>1</v>
       </c>
       <c r="D149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149">
         <v>7</v>
@@ -10767,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="R149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S149" t="b">
         <v>1</v>
@@ -10776,7 +10776,7 @@
         <v>7</v>
       </c>
       <c r="U149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V149">
         <v>7</v>
@@ -10796,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="D150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>7</v>
@@ -10832,7 +10832,7 @@
         <v>1</v>
       </c>
       <c r="R150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S150" t="b">
         <v>1</v>
@@ -11027,7 +11027,7 @@
         <v>0</v>
       </c>
       <c r="R153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S153" t="b">
         <v>1</v>
@@ -11056,7 +11056,7 @@
         <v>1</v>
       </c>
       <c r="D154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="R154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S154" t="b">
         <v>1</v>
@@ -11101,7 +11101,7 @@
         <v>7</v>
       </c>
       <c r="U154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V154">
         <v>7</v>
@@ -11157,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="R155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S155" t="b">
         <v>1</v>
@@ -11222,7 +11222,7 @@
         <v>0</v>
       </c>
       <c r="R156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S156" t="b">
         <v>1</v>
@@ -11287,7 +11287,7 @@
         <v>0</v>
       </c>
       <c r="R157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S157" t="b">
         <v>1</v>
@@ -11316,7 +11316,7 @@
         <v>1</v>
       </c>
       <c r="D158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158">
         <v>7</v>
@@ -11352,7 +11352,7 @@
         <v>1</v>
       </c>
       <c r="R158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S158" t="b">
         <v>1</v>
@@ -11547,7 +11547,7 @@
         <v>0</v>
       </c>
       <c r="R161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S161" t="b">
         <v>1</v>
@@ -11612,7 +11612,7 @@
         <v>0</v>
       </c>
       <c r="R162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S162" t="b">
         <v>0</v>
@@ -11745,7 +11745,7 @@
         <v>0</v>
       </c>
       <c r="S164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T164">
         <v>5</v>
@@ -11807,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="R165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S165" t="b">
         <v>1</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="R167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T167">
         <v>7</v>
@@ -12002,7 +12002,7 @@
         <v>0</v>
       </c>
       <c r="R168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S168" t="b">
         <v>1</v>
@@ -12067,7 +12067,7 @@
         <v>0</v>
       </c>
       <c r="R169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S169" t="b">
         <v>0</v>
@@ -12132,7 +12132,7 @@
         <v>0</v>
       </c>
       <c r="R170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S170" t="b">
         <v>0</v>
@@ -12197,7 +12197,7 @@
         <v>0</v>
       </c>
       <c r="R171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S171" t="b">
         <v>1</v>
@@ -12327,10 +12327,10 @@
         <v>0</v>
       </c>
       <c r="R173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T173">
         <v>7</v>
@@ -12392,7 +12392,7 @@
         <v>0</v>
       </c>
       <c r="R174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S174" t="b">
         <v>1</v>
@@ -12522,10 +12522,10 @@
         <v>1</v>
       </c>
       <c r="R176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T176">
         <v>7</v>
@@ -12587,10 +12587,10 @@
         <v>0</v>
       </c>
       <c r="R177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T177">
         <v>7</v>
@@ -12616,7 +12616,7 @@
         <v>5</v>
       </c>
       <c r="D178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>7</v>
@@ -12652,7 +12652,7 @@
         <v>1</v>
       </c>
       <c r="R178" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S178" t="b">
         <v>1</v>
@@ -12661,7 +12661,7 @@
         <v>7</v>
       </c>
       <c r="U178">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="V178">
         <v>7</v>
@@ -12717,10 +12717,10 @@
         <v>0</v>
       </c>
       <c r="R179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T179">
         <v>7</v>
@@ -12811,7 +12811,7 @@
         <v>5</v>
       </c>
       <c r="D181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181">
         <v>7</v>
@@ -12847,7 +12847,7 @@
         <v>1</v>
       </c>
       <c r="R181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S181" t="b">
         <v>1</v>
@@ -12856,7 +12856,7 @@
         <v>7</v>
       </c>
       <c r="U181">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V181">
         <v>7</v>
@@ -12912,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="R182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S182" t="b">
         <v>1</v>
@@ -12977,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="R183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S183" t="b">
         <v>1</v>
@@ -13042,7 +13042,7 @@
         <v>0</v>
       </c>
       <c r="R184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S184" t="b">
         <v>1</v>
@@ -13172,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="R186" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S186" t="b">
         <v>1</v>
@@ -13201,7 +13201,7 @@
         <v>7</v>
       </c>
       <c r="D187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>7</v>
@@ -13237,7 +13237,7 @@
         <v>1</v>
       </c>
       <c r="R187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S187" t="b">
         <v>1</v>
@@ -13246,7 +13246,7 @@
         <v>7</v>
       </c>
       <c r="U187">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V187">
         <v>7</v>
@@ -13266,7 +13266,7 @@
         <v>7</v>
       </c>
       <c r="D188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>1</v>
       </c>
       <c r="R188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S188" t="b">
         <v>1</v>
@@ -13311,7 +13311,7 @@
         <v>7</v>
       </c>
       <c r="U188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V188">
         <v>7</v>
@@ -13331,7 +13331,7 @@
         <v>7</v>
       </c>
       <c r="D189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E189">
         <v>7</v>
@@ -13367,7 +13367,7 @@
         <v>1</v>
       </c>
       <c r="R189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S189" t="b">
         <v>1</v>
@@ -13376,7 +13376,7 @@
         <v>7</v>
       </c>
       <c r="U189">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V189">
         <v>7</v>
@@ -13396,7 +13396,7 @@
         <v>7</v>
       </c>
       <c r="D190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190">
         <v>7</v>
@@ -13432,7 +13432,7 @@
         <v>1</v>
       </c>
       <c r="R190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S190" t="b">
         <v>1</v>
@@ -13441,7 +13441,7 @@
         <v>7</v>
       </c>
       <c r="U190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V190">
         <v>7</v>
@@ -13526,7 +13526,7 @@
         <v>7</v>
       </c>
       <c r="D192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>7</v>
@@ -13562,7 +13562,7 @@
         <v>1</v>
       </c>
       <c r="R192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S192" t="b">
         <v>1</v>
@@ -13571,7 +13571,7 @@
         <v>7</v>
       </c>
       <c r="U192">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V192">
         <v>7</v>
@@ -13591,7 +13591,7 @@
         <v>7</v>
       </c>
       <c r="D193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193">
         <v>7</v>
@@ -13627,7 +13627,7 @@
         <v>1</v>
       </c>
       <c r="R193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S193" t="b">
         <v>1</v>
@@ -13636,7 +13636,7 @@
         <v>7</v>
       </c>
       <c r="U193">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V193">
         <v>7</v>
@@ -13656,7 +13656,7 @@
         <v>7</v>
       </c>
       <c r="D194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194">
         <v>7</v>
@@ -13692,7 +13692,7 @@
         <v>1</v>
       </c>
       <c r="R194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S194" t="b">
         <v>1</v>
@@ -13701,7 +13701,7 @@
         <v>7</v>
       </c>
       <c r="U194">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V194">
         <v>7</v>
@@ -13721,7 +13721,7 @@
         <v>7</v>
       </c>
       <c r="D195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195">
         <v>7</v>
@@ -13757,7 +13757,7 @@
         <v>1</v>
       </c>
       <c r="R195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S195" t="b">
         <v>1</v>
@@ -13766,7 +13766,7 @@
         <v>7</v>
       </c>
       <c r="U195">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V195">
         <v>7</v>
@@ -13786,7 +13786,7 @@
         <v>7</v>
       </c>
       <c r="D196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196">
         <v>7</v>
@@ -13822,7 +13822,7 @@
         <v>1</v>
       </c>
       <c r="R196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S196" t="b">
         <v>1</v>
@@ -13831,7 +13831,7 @@
         <v>7</v>
       </c>
       <c r="U196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V196">
         <v>7</v>
@@ -13981,7 +13981,7 @@
         <v>7</v>
       </c>
       <c r="D199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E199">
         <v>7</v>
@@ -14017,7 +14017,7 @@
         <v>1</v>
       </c>
       <c r="R199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S199" t="b">
         <v>1</v>
@@ -14026,7 +14026,7 @@
         <v>7</v>
       </c>
       <c r="U199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V199">
         <v>7</v>
@@ -14111,7 +14111,7 @@
         <v>7</v>
       </c>
       <c r="D201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E201">
         <v>7</v>
@@ -14147,7 +14147,7 @@
         <v>1</v>
       </c>
       <c r="R201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S201" t="b">
         <v>1</v>
@@ -14156,7 +14156,7 @@
         <v>7</v>
       </c>
       <c r="U201">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V201">
         <v>7</v>
@@ -14176,7 +14176,7 @@
         <v>7</v>
       </c>
       <c r="D202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E202">
         <v>7</v>
@@ -14212,7 +14212,7 @@
         <v>1</v>
       </c>
       <c r="R202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S202" t="b">
         <v>1</v>
@@ -14221,7 +14221,7 @@
         <v>7</v>
       </c>
       <c r="U202">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V202">
         <v>7</v>
@@ -14241,7 +14241,7 @@
         <v>7</v>
       </c>
       <c r="D203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E203">
         <v>7</v>
@@ -14277,7 +14277,7 @@
         <v>1</v>
       </c>
       <c r="R203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S203" t="b">
         <v>1</v>
@@ -14286,7 +14286,7 @@
         <v>7</v>
       </c>
       <c r="U203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V203">
         <v>7</v>
@@ -14306,7 +14306,7 @@
         <v>7</v>
       </c>
       <c r="D204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204">
         <v>7</v>
@@ -14342,7 +14342,7 @@
         <v>1</v>
       </c>
       <c r="R204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S204" t="b">
         <v>1</v>
@@ -14351,7 +14351,7 @@
         <v>7</v>
       </c>
       <c r="U204">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V204">
         <v>7</v>
@@ -14371,7 +14371,7 @@
         <v>7</v>
       </c>
       <c r="D205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>7</v>
@@ -14407,7 +14407,7 @@
         <v>1</v>
       </c>
       <c r="R205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S205" t="b">
         <v>1</v>
@@ -14416,7 +14416,7 @@
         <v>7</v>
       </c>
       <c r="U205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V205">
         <v>7</v>
@@ -14436,7 +14436,7 @@
         <v>7</v>
       </c>
       <c r="D206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206">
         <v>7</v>
@@ -14472,7 +14472,7 @@
         <v>1</v>
       </c>
       <c r="R206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S206" t="b">
         <v>1</v>
@@ -14481,7 +14481,7 @@
         <v>7</v>
       </c>
       <c r="U206">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V206">
         <v>7</v>
@@ -14501,7 +14501,7 @@
         <v>7</v>
       </c>
       <c r="D207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207">
         <v>7</v>
@@ -14537,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="R207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S207" t="b">
         <v>1</v>
@@ -14546,7 +14546,7 @@
         <v>7</v>
       </c>
       <c r="U207">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V207">
         <v>7</v>

--- a/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_glass.xlsx
+++ b/codigo/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_glass.xlsx
@@ -88,10 +88,10 @@
     <t>cant_min_en_p_elegido</t>
   </si>
   <si>
-    <t>D35_R35_Pentropia</t>
+    <t>PRD35_PR35_CPent_UD080_PE45</t>
   </si>
   <si>
-    <t>D35_R35_Pproporcion</t>
+    <t>PRD35_PR35_CPprop_UD080_Ppp041</t>
   </si>
   <si>
     <t>proporcion</t>
